--- a/Tampa Vendor Bench.xlsx
+++ b/Tampa Vendor Bench.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="510">
   <si>
     <t xml:space="preserve">Tampa Vendor Bench</t>
   </si>
@@ -250,6 +250,654 @@
     <t xml:space="preserve">Does drywall, paint, fixtures, fences. Will not touch panel or pipe cuts.</t>
   </si>
   <si>
+    <t xml:space="preserve">Emmanuel Fenelon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenelon Handyman Services LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(786) 509-5555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fenelonhandymanservices.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (handyman, under $1k jobs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None (handyman exemption)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a, handyman exemption (jobs under $1,000, no plumbing/electrical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No policy or exemption on file (FL DWC, 9/8/2026). Ask for proof before first job.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat-rate per job, 2-hr minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prompt scheduling per reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thumbtack + Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-person crew, all of Hillsborough + Pinellas/Pasco. Fully insured, COI on request. Routes plumbing/electrical to licensed partners. Serves landlords and PM jobs. Bilingual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilfredo Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WL Handyman Service LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 330-0356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wlhandymanservice.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call for quote, free estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same or next day advertised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yelp + Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Tampa owner-operator since 2019, covers Tampa to Brandon/Riverview and Pinellas. Registered and insured. Explicit landlord turnover service, rent-ready in 3-5 days. Ask for COI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin (owner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampa Sarasota Handyman, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 733-0052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tampasarasotahandyman.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup (South Shore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call for quote, no-surprise written quotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google + Angi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverview-based, best for South Shore: Riverview, Brandon, Apollo Beach, Ruskin, Sun City Center. $1M liability stated. Rental turnover and make-ready service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Barnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Barnes Handyman Services LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 390-3410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.handymangeorgebarnes.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (states not a licensed contractor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free in-home estimate; beats or matches written estimates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBB + Yelp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Tampa / Wesley Chapel / Lutz corridor, in business since 1980. One-year labor guarantee. Insurance NOT stated on site, get a COI before first job. Works with property managers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Coughlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Handyman (Citrus Park / Keystone) - franchise price reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 694-1210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mrhandyman.com/citrus-park-keystone/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference (franchise/large shop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGC1513681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cert General Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09, Current/Active, exp 08/31/2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not checked (reference row)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~$158 first hour, then ~$108/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$50 service fee included in first hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBB + HomeAdvisor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference row: what franchise pricing looks like. A good independent lands 30-50% under this on the same punch list. Sister franchises cover Brandon and Lutz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experts Plumbing Services, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-363-9726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://expertsplumbingservices.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFC1428527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cert Plumbing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not checked yet; request COI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$105 service fee, waived if work done; drain stoppage $250-350; electric water heater installed from $1,205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$105, waived with work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon-Fri 7-5, no weekends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google + BBB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Tampa shop, all Hillsborough. Only indie with published flat rates. Property-management testimonial on site. No after-hours, pair with a 24/7 backup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roger (owner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llona Plumbing, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-477-1870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://llonaplumbing.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup (weekends)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFC1431902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$180/hr labor + $50 sewer machine; most stoppages under $250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 hrs Fri-Sun; Mon-Thu 8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family-owned since 2004, West Tampa shop, covers Hillsborough/Pinellas/Pasco/Manatee. Weekend 24-hr coverage makes this the emergency backup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthony Dang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCA Plumbing Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-780-2222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alcaplumbinginc.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup (North)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFC1426773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tub stoppage $280; main sewer line $320-350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 days, 7am-7pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-operated since 2005, Wesley Chapel base, best for North Tampa / New Tampa / Pasco-line houses. Owner answers the phone and supervises jobs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerry Calhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son of a Plumber Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-368-6028 (call or text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sonofaplumberinc.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFC1430455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call or text for quote; free second opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon-Fri 8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yelp + Nextdoor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-man master plumber, Wesley Chapel / Temple Terrace / Land O Lakes. Cheapest structure (no dispatcher, no trucks to feed) but one person means no backup. Good water-heater swap reputation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dave Cass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cass Plumbing, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-265-9200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cassplumbingtampabay.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidate (volume)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFC057412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call for quote; no trip fee; free estimates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None advertised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBB + Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bigger family shop since 2000, Tampa + Brandon offices, multiple trucks. Property managers in reviews cite fast tenant response and documentation. The volume-rate candidate for 60+ doors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roto-Rooter Tampa - franchise price reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-980-6000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rotorooter.com/tampa/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFC1429911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drain cleaning $225-600; after-hours +$100-200; reviews cite $560 holiday drain call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None, baked into flat rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7/365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference row. Competent and fast, consistently 'pricey' in reviews, water-restoration upsell team follows the plumber. Member of Bay Area Apartment Association.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christopher Groves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groves Electric, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-789-3400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.groveselectricinc.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC13011132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cert Electrical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free quotes, no trip charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner on site within the hour per reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family-run South Tampa shop since 1998. Best value signal of the group: no trip charge and reviews cite 'a lot done in one hour'. Tampa proper, not the far suburbs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Lemons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Force Electric, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-251-5559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.forceelectricservice.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC0001712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat rate per job, quoted before work; free estimates; plan members 15% off + no dispatch fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispatch fee for non-members, amount unpublished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google + Yelp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since 1990, Carrollwood / Dale Mabry base, licensed Hillsborough + Pinellas + Pasco. Reviews say quotes come in under competitors. Background-checked techs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Levinus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodus Electric Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-444-4445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.exoduselectric.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup (portfolio plan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC13006236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnostic fee (unpublished), free estimates; after-hours rates apply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After-hours + weekend emergency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The portfolio candidate: offers a written Property Management Maintenance Agreement (turnover, emergencies, annual inspections). Tampa + Brandon offices, 75-mile radius. Since 2007.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Tracy (owner); DBPR qualifier Robert Fistilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Bay Electric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-897-2665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lightningbayelectric.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC13013571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modest diagnostic fee applied to repair; firm price before work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-hour emergency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New company (2024) but courts landlords directly: reviews from a PM running 42 properties. Riverview / East Hillsborough. Ask who the license qualifier is, the DBPR name differs from the owner on the site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houle family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small Jobs Electric, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-968-5856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.smalljobselectric.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidate (after-hours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC0003040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat rate; $49 service fee applied to work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$49 + $29 dispatch (waived for new customers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBB + Angi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-year residential shop, very high volume, 24/7. Reliable backup, but repeat reviews say flat-rate quotes run high. Use for after-hours, not for the everyday call.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mister Sparky of Tampa - franchise price reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">813-328-7210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mistersparky.com/tampa/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC13008384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat rate; trip charge waived for club members; older complaint cites $59 service fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference row. Fast and professional; franchise-wide complaints center on high flat rates and panel/surge upsells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hebert family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3H AC of Tampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 979-4208 (call or text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://3hac.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup (maintenance plan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMC1249567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cert Mechanical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance plan $195/system/yr, 2 visits incl. coil clean, 10% off repairs, multi-system discounts; free phone troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon-Fri 7:30-7:30, weekends 8-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family shop since 2002, North Tampa, Hillsborough/Pinellas/Pasco. Has a dedicated property-management HVAC page with per-system records. The portfolio maintenance-plan candidate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolando Mojarrieta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolando's H.V.A.C., LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 373-6804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rolandoshvac.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC1820272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cert Air Conditioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$125 diagnostic, waived with repair; full system replacement $6,000-12,000 published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$125, waived with repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency repair advertised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-operated since 2019, West Tampa, 5 counties. Huge review volume with a 'no upsell' theme. Publishes replacement price ranges, rare in this trade. Best everyday repair call.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Fontana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontana Brothers Heating &amp; Air Conditioning, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 252-1226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fontanabrothersair.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC1817303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call for quote; club plan 2 tune-ups/yr + 15% off parts and labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three brothers, West Tampa, since 2012, 5 counties. Reviews repeat 'honest' and 'reasonable rates'. No landlord program but a solid backup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morales family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Therapist Cooling, Heating, and Plumbing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 343-2212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://callhometherapist.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC1819196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cert Air Conditioning (also CFC1431159 plumbing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$89 tune-up promo; plans $120/$240/$480 per system/yr; $279 service-call minimum once repair approved, $120/hr after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Free diagnosis' but $279 minimum applies when work is approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 dispatch, no after-hours surcharge advertised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Tampa, since 2017, HVAC + plumbing under one roof. Explicit 'landlord and property manager' multi-property discount. Pricing pages contradict each other, pin the numbers down by phone before comparing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Maalouf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampa AC Services Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 993-4669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tampa-acservices.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC1822145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance plan $150/system/yr (1 visit), 10% off parts and labor, no overtime fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open 24 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youngest company here (2022), North Tampa. Lowest published plan price, thin third-party review depth. Trial-job candidate, not a primary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IERNA's Heating &amp; Cooling - large-shop price reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(813) 578-7113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.iernaair.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC1822278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnostic fee unpublished, waived with repair; reviews cite $89 and a $413 diagnostic complaint; membership 15% off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-hour support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference row: 100 employees, 50 trucks, HVAC + plumbing + electrical. Responsive, but recurring complaints about surprise diagnostic charges and upsell pressure.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Date</t>
   </si>
   <si>
@@ -331,9 +979,6 @@
     <t xml:space="preserve">No water / major leak / burst pipe</t>
   </si>
   <si>
-    <t xml:space="preserve">Plumber</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yes. Any pipe cutting or drain alteration.</t>
   </si>
   <si>
@@ -415,9 +1060,6 @@
     <t xml:space="preserve">No power to whole unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Electrician</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yes.</t>
   </si>
   <si>
@@ -452,9 +1094,6 @@
   </si>
   <si>
     <t xml:space="preserve">AC not cooling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVAC</t>
   </si>
   <si>
     <t xml:space="preserve">Yes. Refrigerant and electrical work need a license.</t>
@@ -999,7 +1638,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1015,13 +1654,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEAF2E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF9C4"/>
         <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2E3"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1074,7 +1719,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1124,6 +1769,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1236,7 +1889,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFEAF2E3"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -2116,7 +2769,7 @@
       </c>
       <c r="L2" s="9" t="n">
         <f aca="true">IF(K2="","",K2-TODAY())</f>
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>68</v>
@@ -2153,34 +2806,62 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="14"/>
       <c r="L3" s="9" t="str">
         <f aca="true">IF(K3="","",K3-TODAY())</f>
         <v/>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="9" t="str">
+      <c r="M3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="R3" s="9" t="n">
         <f aca="false">IF(A3="","",COUNTIF('Job Log'!$E:$E,A3))</f>
-        <v/>
-      </c>
-      <c r="S3" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S3" s="10" t="n">
         <f aca="false">IF(A3="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T3" s="11" t="str">
         <f aca="false">IF(OR(A3="",COUNTIFS('Job Log'!$E:$E,A3,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A3,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2190,36 +2871,66 @@
         <f aca="false">IF(OR(A3="",COUNTIF('Job Log'!$E:$E,A3)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A3)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="V3" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="14"/>
       <c r="L4" s="9" t="str">
         <f aca="true">IF(K4="","",K4-TODAY())</f>
         <v/>
       </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="9" t="str">
+      <c r="M4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="R4" s="9" t="n">
         <f aca="false">IF(A4="","",COUNTIF('Job Log'!$E:$E,A4))</f>
-        <v/>
-      </c>
-      <c r="S4" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S4" s="10" t="n">
         <f aca="false">IF(A4="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T4" s="11" t="str">
         <f aca="false">IF(OR(A4="",COUNTIFS('Job Log'!$E:$E,A4,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A4,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2229,36 +2940,64 @@
         <f aca="false">IF(OR(A4="",COUNTIF('Job Log'!$E:$E,A4)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A4)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="V4" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="14"/>
       <c r="L5" s="9" t="str">
         <f aca="true">IF(K5="","",K5-TODAY())</f>
         <v/>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="9" t="str">
+      <c r="M5" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="R5" s="9" t="n">
         <f aca="false">IF(A5="","",COUNTIF('Job Log'!$E:$E,A5))</f>
-        <v/>
-      </c>
-      <c r="S5" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10" t="n">
         <f aca="false">IF(A5="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T5" s="11" t="str">
         <f aca="false">IF(OR(A5="",COUNTIFS('Job Log'!$E:$E,A5,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A5,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2268,36 +3007,64 @@
         <f aca="false">IF(OR(A5="",COUNTIF('Job Log'!$E:$E,A5)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A5)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="V5" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="14"/>
       <c r="L6" s="9" t="str">
         <f aca="true">IF(K6="","",K6-TODAY())</f>
         <v/>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="9" t="str">
+      <c r="M6" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="R6" s="9" t="n">
         <f aca="false">IF(A6="","",COUNTIF('Job Log'!$E:$E,A6))</f>
-        <v/>
-      </c>
-      <c r="S6" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S6" s="10" t="n">
         <f aca="false">IF(A6="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A6))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T6" s="11" t="str">
         <f aca="false">IF(OR(A6="",COUNTIFS('Job Log'!$E:$E,A6,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A6,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2307,36 +3074,66 @@
         <f aca="false">IF(OR(A6="",COUNTIF('Job Log'!$E:$E,A6)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A6)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="V6" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K7" s="14"/>
       <c r="L7" s="9" t="str">
         <f aca="true">IF(K7="","",K7-TODAY())</f>
         <v/>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="9" t="str">
+      <c r="M7" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="R7" s="9" t="n">
         <f aca="false">IF(A7="","",COUNTIF('Job Log'!$E:$E,A7))</f>
-        <v/>
-      </c>
-      <c r="S7" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10" t="n">
         <f aca="false">IF(A7="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A7))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T7" s="11" t="str">
         <f aca="false">IF(OR(A7="",COUNTIFS('Job Log'!$E:$E,A7,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A7,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2346,29 +3143,59 @@
         <f aca="false">IF(OR(A7="",COUNTIF('Job Log'!$E:$E,A7)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A7)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+      <c r="V7" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="14"/>
       <c r="L8" s="9" t="str">
         <f aca="true">IF(K8="","",K8-TODAY())</f>
         <v/>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
+      <c r="M8" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="R8" s="9" t="str">
         <f aca="false">IF(A8="","",COUNTIF('Job Log'!$E:$E,A8))</f>
         <v/>
@@ -2385,36 +3212,66 @@
         <f aca="false">IF(OR(A8="",COUNTIF('Job Log'!$E:$E,A8)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A8)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="V8" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K9" s="14"/>
       <c r="L9" s="9" t="str">
         <f aca="true">IF(K9="","",K9-TODAY())</f>
         <v/>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="9" t="str">
+      <c r="M9" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R9" s="9" t="n">
         <f aca="false">IF(A9="","",COUNTIF('Job Log'!$E:$E,A9))</f>
-        <v/>
-      </c>
-      <c r="S9" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S9" s="10" t="n">
         <f aca="false">IF(A9="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A9))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T9" s="11" t="str">
         <f aca="false">IF(OR(A9="",COUNTIFS('Job Log'!$E:$E,A9,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A9,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2424,36 +3281,66 @@
         <f aca="false">IF(OR(A9="",COUNTIF('Job Log'!$E:$E,A9)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A9)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="V9" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" s="14"/>
       <c r="L10" s="9" t="str">
         <f aca="true">IF(K10="","",K10-TODAY())</f>
         <v/>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="9" t="str">
+      <c r="M10" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R10" s="9" t="n">
         <f aca="false">IF(A10="","",COUNTIF('Job Log'!$E:$E,A10))</f>
-        <v/>
-      </c>
-      <c r="S10" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S10" s="10" t="n">
         <f aca="false">IF(A10="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T10" s="11" t="str">
         <f aca="false">IF(OR(A10="",COUNTIFS('Job Log'!$E:$E,A10,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A10,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2463,36 +3350,66 @@
         <f aca="false">IF(OR(A10="",COUNTIF('Job Log'!$E:$E,A10)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A10)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="V10" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="14"/>
       <c r="L11" s="9" t="str">
         <f aca="true">IF(K11="","",K11-TODAY())</f>
         <v/>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="9" t="str">
+      <c r="M11" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="R11" s="9" t="n">
         <f aca="false">IF(A11="","",COUNTIF('Job Log'!$E:$E,A11))</f>
-        <v/>
-      </c>
-      <c r="S11" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S11" s="10" t="n">
         <f aca="false">IF(A11="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A11))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T11" s="11" t="str">
         <f aca="false">IF(OR(A11="",COUNTIFS('Job Log'!$E:$E,A11,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A11,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2502,36 +3419,68 @@
         <f aca="false">IF(OR(A11="",COUNTIF('Job Log'!$E:$E,A11)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A11)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="V11" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="14"/>
       <c r="L12" s="9" t="str">
         <f aca="true">IF(K12="","",K12-TODAY())</f>
         <v/>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="9" t="str">
+      <c r="M12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q12" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="R12" s="9" t="n">
         <f aca="false">IF(A12="","",COUNTIF('Job Log'!$E:$E,A12))</f>
-        <v/>
-      </c>
-      <c r="S12" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S12" s="10" t="n">
         <f aca="false">IF(A12="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A12))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T12" s="11" t="str">
         <f aca="false">IF(OR(A12="",COUNTIFS('Job Log'!$E:$E,A12,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A12,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2541,29 +3490,59 @@
         <f aca="false">IF(OR(A12="",COUNTIF('Job Log'!$E:$E,A12)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A12)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="V12" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13" s="14"/>
       <c r="L13" s="9" t="str">
         <f aca="true">IF(K13="","",K13-TODAY())</f>
         <v/>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="M13" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="R13" s="9" t="str">
         <f aca="false">IF(A13="","",COUNTIF('Job Log'!$E:$E,A13))</f>
         <v/>
@@ -2580,36 +3559,68 @@
         <f aca="false">IF(OR(A13="",COUNTIF('Job Log'!$E:$E,A13)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A13)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="V13" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="14"/>
       <c r="L14" s="9" t="str">
         <f aca="true">IF(K14="","",K14-TODAY())</f>
         <v/>
       </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="9" t="str">
+      <c r="M14" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q14" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="R14" s="9" t="n">
         <f aca="false">IF(A14="","",COUNTIF('Job Log'!$E:$E,A14))</f>
-        <v/>
-      </c>
-      <c r="S14" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S14" s="10" t="n">
         <f aca="false">IF(A14="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A14))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T14" s="11" t="str">
         <f aca="false">IF(OR(A14="",COUNTIFS('Job Log'!$E:$E,A14,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A14,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2619,36 +3630,66 @@
         <f aca="false">IF(OR(A14="",COUNTIF('Job Log'!$E:$E,A14)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A14)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="V14" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="14"/>
       <c r="L15" s="9" t="str">
         <f aca="true">IF(K15="","",K15-TODAY())</f>
         <v/>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="9" t="str">
+      <c r="M15" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="R15" s="9" t="n">
         <f aca="false">IF(A15="","",COUNTIF('Job Log'!$E:$E,A15))</f>
-        <v/>
-      </c>
-      <c r="S15" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S15" s="10" t="n">
         <f aca="false">IF(A15="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A15))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T15" s="11" t="str">
         <f aca="false">IF(OR(A15="",COUNTIFS('Job Log'!$E:$E,A15,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A15,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2658,36 +3699,66 @@
         <f aca="false">IF(OR(A15="",COUNTIF('Job Log'!$E:$E,A15)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A15)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="V15" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" s="14"/>
       <c r="L16" s="9" t="str">
         <f aca="true">IF(K16="","",K16-TODAY())</f>
         <v/>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="9" t="str">
+      <c r="M16" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="R16" s="9" t="n">
         <f aca="false">IF(A16="","",COUNTIF('Job Log'!$E:$E,A16))</f>
-        <v/>
-      </c>
-      <c r="S16" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S16" s="10" t="n">
         <f aca="false">IF(A16="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A16))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T16" s="11" t="str">
         <f aca="false">IF(OR(A16="",COUNTIFS('Job Log'!$E:$E,A16,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A16,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2697,36 +3768,66 @@
         <f aca="false">IF(OR(A16="",COUNTIF('Job Log'!$E:$E,A16)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A16)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="V16" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K17" s="14"/>
       <c r="L17" s="9" t="str">
         <f aca="true">IF(K17="","",K17-TODAY())</f>
         <v/>
       </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="9" t="str">
+      <c r="M17" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R17" s="9" t="n">
         <f aca="false">IF(A17="","",COUNTIF('Job Log'!$E:$E,A17))</f>
-        <v/>
-      </c>
-      <c r="S17" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S17" s="10" t="n">
         <f aca="false">IF(A17="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A17))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T17" s="11" t="str">
         <f aca="false">IF(OR(A17="",COUNTIFS('Job Log'!$E:$E,A17,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A17,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2736,36 +3837,68 @@
         <f aca="false">IF(OR(A17="",COUNTIF('Job Log'!$E:$E,A17)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A17)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="V17" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" s="14"/>
       <c r="L18" s="9" t="str">
         <f aca="true">IF(K18="","",K18-TODAY())</f>
         <v/>
       </c>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="9" t="str">
+      <c r="M18" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="R18" s="9" t="n">
         <f aca="false">IF(A18="","",COUNTIF('Job Log'!$E:$E,A18))</f>
-        <v/>
-      </c>
-      <c r="S18" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S18" s="10" t="n">
         <f aca="false">IF(A18="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A18))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T18" s="11" t="str">
         <f aca="false">IF(OR(A18="",COUNTIFS('Job Log'!$E:$E,A18,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A18,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2775,29 +3908,57 @@
         <f aca="false">IF(OR(A18="",COUNTIF('Job Log'!$E:$E,A18)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A18)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="V18" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="14"/>
       <c r="L19" s="9" t="str">
         <f aca="true">IF(K19="","",K19-TODAY())</f>
         <v/>
       </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="M19" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>235</v>
+      </c>
       <c r="R19" s="9" t="str">
         <f aca="false">IF(A19="","",COUNTIF('Job Log'!$E:$E,A19))</f>
         <v/>
@@ -2814,36 +3975,66 @@
         <f aca="false">IF(OR(A19="",COUNTIF('Job Log'!$E:$E,A19)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A19)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="V19" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K20" s="14"/>
       <c r="L20" s="9" t="str">
         <f aca="true">IF(K20="","",K20-TODAY())</f>
         <v/>
       </c>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="9" t="str">
+      <c r="M20" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="9" t="n">
         <f aca="false">IF(A20="","",COUNTIF('Job Log'!$E:$E,A20))</f>
-        <v/>
-      </c>
-      <c r="S20" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S20" s="10" t="n">
         <f aca="false">IF(A20="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A20))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T20" s="11" t="str">
         <f aca="false">IF(OR(A20="",COUNTIFS('Job Log'!$E:$E,A20,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A20,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2853,36 +4044,68 @@
         <f aca="false">IF(OR(A20="",COUNTIF('Job Log'!$E:$E,A20)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A20)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="V20" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21" s="14"/>
       <c r="L21" s="9" t="str">
         <f aca="true">IF(K21="","",K21-TODAY())</f>
         <v/>
       </c>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="9" t="str">
+      <c r="M21" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R21" s="9" t="n">
         <f aca="false">IF(A21="","",COUNTIF('Job Log'!$E:$E,A21))</f>
-        <v/>
-      </c>
-      <c r="S21" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S21" s="10" t="n">
         <f aca="false">IF(A21="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A21))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T21" s="11" t="str">
         <f aca="false">IF(OR(A21="",COUNTIFS('Job Log'!$E:$E,A21,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A21,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2892,36 +4115,64 @@
         <f aca="false">IF(OR(A21="",COUNTIF('Job Log'!$E:$E,A21)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A21)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="V21" s="13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22" s="14"/>
       <c r="L22" s="9" t="str">
         <f aca="true">IF(K22="","",K22-TODAY())</f>
         <v/>
       </c>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="9" t="str">
+      <c r="M22" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="R22" s="9" t="n">
         <f aca="false">IF(A22="","",COUNTIF('Job Log'!$E:$E,A22))</f>
-        <v/>
-      </c>
-      <c r="S22" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S22" s="10" t="n">
         <f aca="false">IF(A22="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A22))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T22" s="11" t="str">
         <f aca="false">IF(OR(A22="",COUNTIFS('Job Log'!$E:$E,A22,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A22,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2931,36 +4182,68 @@
         <f aca="false">IF(OR(A22="",COUNTIF('Job Log'!$E:$E,A22)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A22)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="V22" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23" s="14"/>
       <c r="L23" s="9" t="str">
         <f aca="true">IF(K23="","",K23-TODAY())</f>
         <v/>
       </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="9" t="str">
+      <c r="M23" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R23" s="9" t="n">
         <f aca="false">IF(A23="","",COUNTIF('Job Log'!$E:$E,A23))</f>
-        <v/>
-      </c>
-      <c r="S23" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S23" s="10" t="n">
         <f aca="false">IF(A23="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A23))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T23" s="11" t="str">
         <f aca="false">IF(OR(A23="",COUNTIFS('Job Log'!$E:$E,A23,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A23,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -2970,36 +4253,66 @@
         <f aca="false">IF(OR(A23="",COUNTIF('Job Log'!$E:$E,A23)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A23)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="V23" s="13" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" s="14"/>
       <c r="L24" s="9" t="str">
         <f aca="true">IF(K24="","",K24-TODAY())</f>
         <v/>
       </c>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="9" t="str">
+      <c r="M24" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R24" s="9" t="n">
         <f aca="false">IF(A24="","",COUNTIF('Job Log'!$E:$E,A24))</f>
-        <v/>
-      </c>
-      <c r="S24" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S24" s="10" t="n">
         <f aca="false">IF(A24="","",SUMIFS('Job Log'!$H:$H,'Job Log'!$E:$E,A24))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T24" s="11" t="str">
         <f aca="false">IF(OR(A24="",COUNTIFS('Job Log'!$E:$E,A24,'Job Log'!$I:$I,"&gt;0")=0),"",AVERAGEIFS('Job Log'!$I:$I,'Job Log'!$E:$E,A24,'Job Log'!$I:$I,"&gt;0"))</f>
@@ -3009,29 +4322,57 @@
         <f aca="false">IF(OR(A24="",COUNTIF('Job Log'!$E:$E,A24)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A24)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="V24" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25" s="14"/>
       <c r="L25" s="9" t="str">
         <f aca="true">IF(K25="","",K25-TODAY())</f>
         <v/>
       </c>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="M25" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q25" s="13" t="s">
+        <v>235</v>
+      </c>
       <c r="R25" s="9" t="str">
         <f aca="false">IF(A25="","",COUNTIF('Job Log'!$E:$E,A25))</f>
         <v/>
@@ -3048,7 +4389,9 @@
         <f aca="false">IF(OR(A25="",COUNTIF('Job Log'!$E:$E,A25)=0),"",SUMPRODUCT(MAX(('Job Log'!$E$2:$E$500=A25)*'Job Log'!$A$2:$A$500)))</f>
         <v/>
       </c>
-      <c r="V25" s="7"/>
+      <c r="V25" s="13" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
@@ -3060,8 +4403,8 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
       <c r="L26" s="9" t="str">
         <f aca="true">IF(K26="","",K26-TODAY())</f>
         <v/>
@@ -3099,8 +4442,8 @@
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
       <c r="L27" s="9" t="str">
         <f aca="true">IF(K27="","",K27-TODAY())</f>
         <v/>
@@ -3138,8 +4481,8 @@
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
       <c r="L28" s="9" t="str">
         <f aca="true">IF(K28="","",K28-TODAY())</f>
         <v/>
@@ -3177,8 +4520,8 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
       <c r="L29" s="9" t="str">
         <f aca="true">IF(K29="","",K29-TODAY())</f>
         <v/>
@@ -3216,8 +4559,8 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
       <c r="L30" s="9" t="str">
         <f aca="true">IF(K30="","",K30-TODAY())</f>
         <v/>
@@ -3255,8 +4598,8 @@
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
       <c r="L31" s="9" t="str">
         <f aca="true">IF(K31="","",K31-TODAY())</f>
         <v/>
@@ -3294,8 +4637,8 @@
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
       <c r="L32" s="9" t="str">
         <f aca="true">IF(K32="","",K32-TODAY())</f>
         <v/>
@@ -3333,8 +4676,8 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
       <c r="L33" s="9" t="str">
         <f aca="true">IF(K33="","",K33-TODAY())</f>
         <v/>
@@ -3372,8 +4715,8 @@
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
       <c r="L34" s="9" t="str">
         <f aca="true">IF(K34="","",K34-TODAY())</f>
         <v/>
@@ -3411,8 +4754,8 @@
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
       <c r="L35" s="9" t="str">
         <f aca="true">IF(K35="","",K35-TODAY())</f>
         <v/>
@@ -3450,8 +4793,8 @@
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
       <c r="L36" s="9" t="str">
         <f aca="true">IF(K36="","",K36-TODAY())</f>
         <v/>
@@ -3489,8 +4832,8 @@
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
       <c r="L37" s="9" t="str">
         <f aca="true">IF(K37="","",K37-TODAY())</f>
         <v/>
@@ -3528,8 +4871,8 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
       <c r="L38" s="9" t="str">
         <f aca="true">IF(K38="","",K38-TODAY())</f>
         <v/>
@@ -3567,8 +4910,8 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
       <c r="L39" s="9" t="str">
         <f aca="true">IF(K39="","",K39-TODAY())</f>
         <v/>
@@ -3606,8 +4949,8 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
       <c r="L40" s="9" t="str">
         <f aca="true">IF(K40="","",K40-TODAY())</f>
         <v/>
@@ -3645,8 +4988,8 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
       <c r="L41" s="9" t="str">
         <f aca="true">IF(K41="","",K41-TODAY())</f>
         <v/>
@@ -3691,7 +5034,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F41" type="list">
-      <formula1>"Primary,Backup,Trial,Retired"</formula1>
+      <formula1>"Primary,Backup,Trial,Candidate,Retired"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G41" type="list">
@@ -3738,43 +5081,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>85</v>
+        <v>300</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3785,7 +5128,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>86</v>
+        <v>302</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>60</v>
@@ -3794,2893 +5137,2893 @@
         <v>58</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="15" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="H2" s="15" t="n">
+      <c r="H2" s="17" t="n">
         <v>110</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>88</v>
+        <v>304</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>88</v>
+        <v>304</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="O2" s="17" t="n">
+        <v>305</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="O2" s="19" t="n">
         <f aca="false">SUM(H2:H500)</f>
         <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="N3" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3" s="17" t="n">
+      <c r="N3" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="O3" s="19" t="n">
         <f aca="true">SUMIFS(H2:H500,A2:A500,"&gt;="&amp;(TODAY()-90))</f>
         <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="N4" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="O4" s="19" t="n">
+      <c r="N4" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="O4" s="21" t="n">
         <f aca="true">COUNTIFS(A2:A500,"&gt;="&amp;(TODAY()-90),H2:H500,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
+      <c r="A5" s="15"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="N5" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="O5" s="17" t="n">
+      <c r="N5" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="O5" s="19" t="n">
         <f aca="false">IF(O4=0,0,O3/O4)</f>
         <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-      <c r="N6" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="O6" s="19" t="n">
+      <c r="N6" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="O6" s="21" t="n">
         <f aca="true">COUNTIFS(A2:A500,"&gt;="&amp;(TODAY()-90),F2:F500,"Emergency")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13"/>
+      <c r="A37" s="15"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13"/>
+      <c r="A38" s="15"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
+      <c r="A39" s="15"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
+      <c r="A40" s="15"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="A41" s="22"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
+      <c r="A42" s="22"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
+      <c r="A43" s="22"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
+      <c r="A44" s="22"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
+      <c r="A45" s="22"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
+      <c r="A46" s="22"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
+      <c r="A47" s="22"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
+      <c r="A48" s="22"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="23"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
+      <c r="A49" s="22"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
+      <c r="A50" s="22"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="20"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
+      <c r="A51" s="22"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="23"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="20"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
+      <c r="A52" s="22"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="20"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
+      <c r="A53" s="22"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="23"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="20"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
+      <c r="A54" s="22"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
+      <c r="A55" s="22"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="23"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="20"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
+      <c r="A56" s="22"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
+      <c r="A57" s="22"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="23"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
+      <c r="A58" s="22"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
+      <c r="A59" s="22"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
+      <c r="A60" s="22"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="23"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="20"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
+      <c r="A61" s="22"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="23"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="20"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
+      <c r="A62" s="22"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="23"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
+      <c r="A63" s="22"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
+      <c r="A64" s="22"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="20"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
+      <c r="A65" s="22"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="23"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="20"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
+      <c r="A66" s="22"/>
+      <c r="G66" s="23"/>
+      <c r="H66" s="23"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="20"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
+      <c r="A67" s="22"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="20"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
+      <c r="A68" s="22"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
+      <c r="A69" s="22"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="23"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="20"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
+      <c r="A70" s="22"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="20"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
+      <c r="A71" s="22"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
+      <c r="A72" s="22"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="20"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
+      <c r="A73" s="22"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="20"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
+      <c r="A74" s="22"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="20"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
+      <c r="A75" s="22"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
+      <c r="A76" s="22"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
+      <c r="A77" s="22"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="20"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
+      <c r="A78" s="22"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="20"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
+      <c r="A79" s="22"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="20"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
+      <c r="A80" s="22"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="23"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="20"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
+      <c r="A81" s="22"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="23"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="20"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
+      <c r="A82" s="22"/>
+      <c r="G82" s="23"/>
+      <c r="H82" s="23"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="20"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
+      <c r="A83" s="22"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="23"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="20"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
+      <c r="A84" s="22"/>
+      <c r="G84" s="23"/>
+      <c r="H84" s="23"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="20"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
+      <c r="A85" s="22"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="20"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
+      <c r="A86" s="22"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="20"/>
-      <c r="G87" s="21"/>
-      <c r="H87" s="21"/>
+      <c r="A87" s="22"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="23"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="20"/>
-      <c r="G88" s="21"/>
-      <c r="H88" s="21"/>
+      <c r="A88" s="22"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="20"/>
-      <c r="G89" s="21"/>
-      <c r="H89" s="21"/>
+      <c r="A89" s="22"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="20"/>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21"/>
+      <c r="A90" s="22"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="23"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="20"/>
-      <c r="G91" s="21"/>
-      <c r="H91" s="21"/>
+      <c r="A91" s="22"/>
+      <c r="G91" s="23"/>
+      <c r="H91" s="23"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="20"/>
-      <c r="G92" s="21"/>
-      <c r="H92" s="21"/>
+      <c r="A92" s="22"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="20"/>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21"/>
+      <c r="A93" s="22"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="20"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
+      <c r="A94" s="22"/>
+      <c r="G94" s="23"/>
+      <c r="H94" s="23"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="20"/>
-      <c r="G95" s="21"/>
-      <c r="H95" s="21"/>
+      <c r="A95" s="22"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="23"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="20"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="21"/>
+      <c r="A96" s="22"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="23"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="20"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
+      <c r="A97" s="22"/>
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="20"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
+      <c r="A98" s="22"/>
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="20"/>
-      <c r="G99" s="21"/>
-      <c r="H99" s="21"/>
+      <c r="A99" s="22"/>
+      <c r="G99" s="23"/>
+      <c r="H99" s="23"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="20"/>
-      <c r="G100" s="21"/>
-      <c r="H100" s="21"/>
+      <c r="A100" s="22"/>
+      <c r="G100" s="23"/>
+      <c r="H100" s="23"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="20"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
+      <c r="A101" s="22"/>
+      <c r="G101" s="23"/>
+      <c r="H101" s="23"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="20"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
+      <c r="A102" s="22"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="20"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
+      <c r="A103" s="22"/>
+      <c r="G103" s="23"/>
+      <c r="H103" s="23"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="20"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
+      <c r="A104" s="22"/>
+      <c r="G104" s="23"/>
+      <c r="H104" s="23"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="20"/>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21"/>
+      <c r="A105" s="22"/>
+      <c r="G105" s="23"/>
+      <c r="H105" s="23"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="20"/>
-      <c r="G106" s="21"/>
-      <c r="H106" s="21"/>
+      <c r="A106" s="22"/>
+      <c r="G106" s="23"/>
+      <c r="H106" s="23"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="20"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
+      <c r="A107" s="22"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="20"/>
-      <c r="G108" s="21"/>
-      <c r="H108" s="21"/>
+      <c r="A108" s="22"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="20"/>
-      <c r="G109" s="21"/>
-      <c r="H109" s="21"/>
+      <c r="A109" s="22"/>
+      <c r="G109" s="23"/>
+      <c r="H109" s="23"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="20"/>
-      <c r="G110" s="21"/>
-      <c r="H110" s="21"/>
+      <c r="A110" s="22"/>
+      <c r="G110" s="23"/>
+      <c r="H110" s="23"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="20"/>
-      <c r="G111" s="21"/>
-      <c r="H111" s="21"/>
+      <c r="A111" s="22"/>
+      <c r="G111" s="23"/>
+      <c r="H111" s="23"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="20"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
+      <c r="A112" s="22"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="23"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="20"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
+      <c r="A113" s="22"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="23"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="20"/>
-      <c r="G114" s="21"/>
-      <c r="H114" s="21"/>
+      <c r="A114" s="22"/>
+      <c r="G114" s="23"/>
+      <c r="H114" s="23"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="20"/>
-      <c r="G115" s="21"/>
-      <c r="H115" s="21"/>
+      <c r="A115" s="22"/>
+      <c r="G115" s="23"/>
+      <c r="H115" s="23"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="20"/>
-      <c r="G116" s="21"/>
-      <c r="H116" s="21"/>
+      <c r="A116" s="22"/>
+      <c r="G116" s="23"/>
+      <c r="H116" s="23"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="20"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21"/>
+      <c r="A117" s="22"/>
+      <c r="G117" s="23"/>
+      <c r="H117" s="23"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="20"/>
-      <c r="G118" s="21"/>
-      <c r="H118" s="21"/>
+      <c r="A118" s="22"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="20"/>
-      <c r="G119" s="21"/>
-      <c r="H119" s="21"/>
+      <c r="A119" s="22"/>
+      <c r="G119" s="23"/>
+      <c r="H119" s="23"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="20"/>
-      <c r="G120" s="21"/>
-      <c r="H120" s="21"/>
+      <c r="A120" s="22"/>
+      <c r="G120" s="23"/>
+      <c r="H120" s="23"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="20"/>
-      <c r="G121" s="21"/>
-      <c r="H121" s="21"/>
+      <c r="A121" s="22"/>
+      <c r="G121" s="23"/>
+      <c r="H121" s="23"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="20"/>
-      <c r="G122" s="21"/>
-      <c r="H122" s="21"/>
+      <c r="A122" s="22"/>
+      <c r="G122" s="23"/>
+      <c r="H122" s="23"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="20"/>
-      <c r="G123" s="21"/>
-      <c r="H123" s="21"/>
+      <c r="A123" s="22"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="20"/>
-      <c r="G124" s="21"/>
-      <c r="H124" s="21"/>
+      <c r="A124" s="22"/>
+      <c r="G124" s="23"/>
+      <c r="H124" s="23"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="20"/>
-      <c r="G125" s="21"/>
-      <c r="H125" s="21"/>
+      <c r="A125" s="22"/>
+      <c r="G125" s="23"/>
+      <c r="H125" s="23"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="20"/>
-      <c r="G126" s="21"/>
-      <c r="H126" s="21"/>
+      <c r="A126" s="22"/>
+      <c r="G126" s="23"/>
+      <c r="H126" s="23"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="20"/>
-      <c r="G127" s="21"/>
-      <c r="H127" s="21"/>
+      <c r="A127" s="22"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="20"/>
-      <c r="G128" s="21"/>
-      <c r="H128" s="21"/>
+      <c r="A128" s="22"/>
+      <c r="G128" s="23"/>
+      <c r="H128" s="23"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="20"/>
-      <c r="G129" s="21"/>
-      <c r="H129" s="21"/>
+      <c r="A129" s="22"/>
+      <c r="G129" s="23"/>
+      <c r="H129" s="23"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="20"/>
-      <c r="G130" s="21"/>
-      <c r="H130" s="21"/>
+      <c r="A130" s="22"/>
+      <c r="G130" s="23"/>
+      <c r="H130" s="23"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="20"/>
-      <c r="G131" s="21"/>
-      <c r="H131" s="21"/>
+      <c r="A131" s="22"/>
+      <c r="G131" s="23"/>
+      <c r="H131" s="23"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="20"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21"/>
+      <c r="A132" s="22"/>
+      <c r="G132" s="23"/>
+      <c r="H132" s="23"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="20"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
+      <c r="A133" s="22"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="23"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="20"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
+      <c r="A134" s="22"/>
+      <c r="G134" s="23"/>
+      <c r="H134" s="23"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="20"/>
-      <c r="G135" s="21"/>
-      <c r="H135" s="21"/>
+      <c r="A135" s="22"/>
+      <c r="G135" s="23"/>
+      <c r="H135" s="23"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="20"/>
-      <c r="G136" s="21"/>
-      <c r="H136" s="21"/>
+      <c r="A136" s="22"/>
+      <c r="G136" s="23"/>
+      <c r="H136" s="23"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="20"/>
-      <c r="G137" s="21"/>
-      <c r="H137" s="21"/>
+      <c r="A137" s="22"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="20"/>
-      <c r="G138" s="21"/>
-      <c r="H138" s="21"/>
+      <c r="A138" s="22"/>
+      <c r="G138" s="23"/>
+      <c r="H138" s="23"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="20"/>
-      <c r="G139" s="21"/>
-      <c r="H139" s="21"/>
+      <c r="A139" s="22"/>
+      <c r="G139" s="23"/>
+      <c r="H139" s="23"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="20"/>
-      <c r="G140" s="21"/>
-      <c r="H140" s="21"/>
+      <c r="A140" s="22"/>
+      <c r="G140" s="23"/>
+      <c r="H140" s="23"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="20"/>
-      <c r="G141" s="21"/>
-      <c r="H141" s="21"/>
+      <c r="A141" s="22"/>
+      <c r="G141" s="23"/>
+      <c r="H141" s="23"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="20"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21"/>
+      <c r="A142" s="22"/>
+      <c r="G142" s="23"/>
+      <c r="H142" s="23"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="20"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
+      <c r="A143" s="22"/>
+      <c r="G143" s="23"/>
+      <c r="H143" s="23"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="20"/>
-      <c r="G144" s="21"/>
-      <c r="H144" s="21"/>
+      <c r="A144" s="22"/>
+      <c r="G144" s="23"/>
+      <c r="H144" s="23"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="20"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="21"/>
+      <c r="A145" s="22"/>
+      <c r="G145" s="23"/>
+      <c r="H145" s="23"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="20"/>
-      <c r="G146" s="21"/>
-      <c r="H146" s="21"/>
+      <c r="A146" s="22"/>
+      <c r="G146" s="23"/>
+      <c r="H146" s="23"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="20"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
+      <c r="A147" s="22"/>
+      <c r="G147" s="23"/>
+      <c r="H147" s="23"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="20"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21"/>
+      <c r="A148" s="22"/>
+      <c r="G148" s="23"/>
+      <c r="H148" s="23"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="20"/>
-      <c r="G149" s="21"/>
-      <c r="H149" s="21"/>
+      <c r="A149" s="22"/>
+      <c r="G149" s="23"/>
+      <c r="H149" s="23"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="20"/>
-      <c r="G150" s="21"/>
-      <c r="H150" s="21"/>
+      <c r="A150" s="22"/>
+      <c r="G150" s="23"/>
+      <c r="H150" s="23"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="20"/>
-      <c r="G151" s="21"/>
-      <c r="H151" s="21"/>
+      <c r="A151" s="22"/>
+      <c r="G151" s="23"/>
+      <c r="H151" s="23"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="20"/>
-      <c r="G152" s="21"/>
-      <c r="H152" s="21"/>
+      <c r="A152" s="22"/>
+      <c r="G152" s="23"/>
+      <c r="H152" s="23"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="20"/>
-      <c r="G153" s="21"/>
-      <c r="H153" s="21"/>
+      <c r="A153" s="22"/>
+      <c r="G153" s="23"/>
+      <c r="H153" s="23"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="20"/>
-      <c r="G154" s="21"/>
-      <c r="H154" s="21"/>
+      <c r="A154" s="22"/>
+      <c r="G154" s="23"/>
+      <c r="H154" s="23"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="20"/>
-      <c r="G155" s="21"/>
-      <c r="H155" s="21"/>
+      <c r="A155" s="22"/>
+      <c r="G155" s="23"/>
+      <c r="H155" s="23"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="20"/>
-      <c r="G156" s="21"/>
-      <c r="H156" s="21"/>
+      <c r="A156" s="22"/>
+      <c r="G156" s="23"/>
+      <c r="H156" s="23"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="20"/>
-      <c r="G157" s="21"/>
-      <c r="H157" s="21"/>
+      <c r="A157" s="22"/>
+      <c r="G157" s="23"/>
+      <c r="H157" s="23"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="20"/>
-      <c r="G158" s="21"/>
-      <c r="H158" s="21"/>
+      <c r="A158" s="22"/>
+      <c r="G158" s="23"/>
+      <c r="H158" s="23"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="20"/>
-      <c r="G159" s="21"/>
-      <c r="H159" s="21"/>
+      <c r="A159" s="22"/>
+      <c r="G159" s="23"/>
+      <c r="H159" s="23"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="20"/>
-      <c r="G160" s="21"/>
-      <c r="H160" s="21"/>
+      <c r="A160" s="22"/>
+      <c r="G160" s="23"/>
+      <c r="H160" s="23"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="20"/>
-      <c r="G161" s="21"/>
-      <c r="H161" s="21"/>
+      <c r="A161" s="22"/>
+      <c r="G161" s="23"/>
+      <c r="H161" s="23"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="20"/>
-      <c r="G162" s="21"/>
-      <c r="H162" s="21"/>
+      <c r="A162" s="22"/>
+      <c r="G162" s="23"/>
+      <c r="H162" s="23"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="20"/>
-      <c r="G163" s="21"/>
-      <c r="H163" s="21"/>
+      <c r="A163" s="22"/>
+      <c r="G163" s="23"/>
+      <c r="H163" s="23"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="20"/>
-      <c r="G164" s="21"/>
-      <c r="H164" s="21"/>
+      <c r="A164" s="22"/>
+      <c r="G164" s="23"/>
+      <c r="H164" s="23"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="20"/>
-      <c r="G165" s="21"/>
-      <c r="H165" s="21"/>
+      <c r="A165" s="22"/>
+      <c r="G165" s="23"/>
+      <c r="H165" s="23"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="20"/>
-      <c r="G166" s="21"/>
-      <c r="H166" s="21"/>
+      <c r="A166" s="22"/>
+      <c r="G166" s="23"/>
+      <c r="H166" s="23"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="20"/>
-      <c r="G167" s="21"/>
-      <c r="H167" s="21"/>
+      <c r="A167" s="22"/>
+      <c r="G167" s="23"/>
+      <c r="H167" s="23"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="20"/>
-      <c r="G168" s="21"/>
-      <c r="H168" s="21"/>
+      <c r="A168" s="22"/>
+      <c r="G168" s="23"/>
+      <c r="H168" s="23"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="20"/>
-      <c r="G169" s="21"/>
-      <c r="H169" s="21"/>
+      <c r="A169" s="22"/>
+      <c r="G169" s="23"/>
+      <c r="H169" s="23"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="20"/>
-      <c r="G170" s="21"/>
-      <c r="H170" s="21"/>
+      <c r="A170" s="22"/>
+      <c r="G170" s="23"/>
+      <c r="H170" s="23"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="20"/>
-      <c r="G171" s="21"/>
-      <c r="H171" s="21"/>
+      <c r="A171" s="22"/>
+      <c r="G171" s="23"/>
+      <c r="H171" s="23"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="20"/>
-      <c r="G172" s="21"/>
-      <c r="H172" s="21"/>
+      <c r="A172" s="22"/>
+      <c r="G172" s="23"/>
+      <c r="H172" s="23"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="20"/>
-      <c r="G173" s="21"/>
-      <c r="H173" s="21"/>
+      <c r="A173" s="22"/>
+      <c r="G173" s="23"/>
+      <c r="H173" s="23"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="20"/>
-      <c r="G174" s="21"/>
-      <c r="H174" s="21"/>
+      <c r="A174" s="22"/>
+      <c r="G174" s="23"/>
+      <c r="H174" s="23"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="20"/>
-      <c r="G175" s="21"/>
-      <c r="H175" s="21"/>
+      <c r="A175" s="22"/>
+      <c r="G175" s="23"/>
+      <c r="H175" s="23"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="20"/>
-      <c r="G176" s="21"/>
-      <c r="H176" s="21"/>
+      <c r="A176" s="22"/>
+      <c r="G176" s="23"/>
+      <c r="H176" s="23"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="20"/>
-      <c r="G177" s="21"/>
-      <c r="H177" s="21"/>
+      <c r="A177" s="22"/>
+      <c r="G177" s="23"/>
+      <c r="H177" s="23"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="20"/>
-      <c r="G178" s="21"/>
-      <c r="H178" s="21"/>
+      <c r="A178" s="22"/>
+      <c r="G178" s="23"/>
+      <c r="H178" s="23"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="20"/>
-      <c r="G179" s="21"/>
-      <c r="H179" s="21"/>
+      <c r="A179" s="22"/>
+      <c r="G179" s="23"/>
+      <c r="H179" s="23"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="20"/>
-      <c r="G180" s="21"/>
-      <c r="H180" s="21"/>
+      <c r="A180" s="22"/>
+      <c r="G180" s="23"/>
+      <c r="H180" s="23"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="20"/>
-      <c r="G181" s="21"/>
-      <c r="H181" s="21"/>
+      <c r="A181" s="22"/>
+      <c r="G181" s="23"/>
+      <c r="H181" s="23"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="20"/>
-      <c r="G182" s="21"/>
-      <c r="H182" s="21"/>
+      <c r="A182" s="22"/>
+      <c r="G182" s="23"/>
+      <c r="H182" s="23"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="20"/>
-      <c r="G183" s="21"/>
-      <c r="H183" s="21"/>
+      <c r="A183" s="22"/>
+      <c r="G183" s="23"/>
+      <c r="H183" s="23"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="20"/>
-      <c r="G184" s="21"/>
-      <c r="H184" s="21"/>
+      <c r="A184" s="22"/>
+      <c r="G184" s="23"/>
+      <c r="H184" s="23"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="20"/>
-      <c r="G185" s="21"/>
-      <c r="H185" s="21"/>
+      <c r="A185" s="22"/>
+      <c r="G185" s="23"/>
+      <c r="H185" s="23"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="20"/>
-      <c r="G186" s="21"/>
-      <c r="H186" s="21"/>
+      <c r="A186" s="22"/>
+      <c r="G186" s="23"/>
+      <c r="H186" s="23"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="20"/>
-      <c r="G187" s="21"/>
-      <c r="H187" s="21"/>
+      <c r="A187" s="22"/>
+      <c r="G187" s="23"/>
+      <c r="H187" s="23"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="20"/>
-      <c r="G188" s="21"/>
-      <c r="H188" s="21"/>
+      <c r="A188" s="22"/>
+      <c r="G188" s="23"/>
+      <c r="H188" s="23"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="20"/>
-      <c r="G189" s="21"/>
-      <c r="H189" s="21"/>
+      <c r="A189" s="22"/>
+      <c r="G189" s="23"/>
+      <c r="H189" s="23"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="20"/>
-      <c r="G190" s="21"/>
-      <c r="H190" s="21"/>
+      <c r="A190" s="22"/>
+      <c r="G190" s="23"/>
+      <c r="H190" s="23"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="20"/>
-      <c r="G191" s="21"/>
-      <c r="H191" s="21"/>
+      <c r="A191" s="22"/>
+      <c r="G191" s="23"/>
+      <c r="H191" s="23"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="20"/>
-      <c r="G192" s="21"/>
-      <c r="H192" s="21"/>
+      <c r="A192" s="22"/>
+      <c r="G192" s="23"/>
+      <c r="H192" s="23"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="20"/>
-      <c r="G193" s="21"/>
-      <c r="H193" s="21"/>
+      <c r="A193" s="22"/>
+      <c r="G193" s="23"/>
+      <c r="H193" s="23"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="20"/>
-      <c r="G194" s="21"/>
-      <c r="H194" s="21"/>
+      <c r="A194" s="22"/>
+      <c r="G194" s="23"/>
+      <c r="H194" s="23"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="20"/>
-      <c r="G195" s="21"/>
-      <c r="H195" s="21"/>
+      <c r="A195" s="22"/>
+      <c r="G195" s="23"/>
+      <c r="H195" s="23"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="20"/>
-      <c r="G196" s="21"/>
-      <c r="H196" s="21"/>
+      <c r="A196" s="22"/>
+      <c r="G196" s="23"/>
+      <c r="H196" s="23"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="20"/>
-      <c r="G197" s="21"/>
-      <c r="H197" s="21"/>
+      <c r="A197" s="22"/>
+      <c r="G197" s="23"/>
+      <c r="H197" s="23"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="20"/>
-      <c r="G198" s="21"/>
-      <c r="H198" s="21"/>
+      <c r="A198" s="22"/>
+      <c r="G198" s="23"/>
+      <c r="H198" s="23"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="20"/>
-      <c r="G199" s="21"/>
-      <c r="H199" s="21"/>
+      <c r="A199" s="22"/>
+      <c r="G199" s="23"/>
+      <c r="H199" s="23"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="20"/>
-      <c r="G200" s="21"/>
-      <c r="H200" s="21"/>
+      <c r="A200" s="22"/>
+      <c r="G200" s="23"/>
+      <c r="H200" s="23"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="20"/>
-      <c r="G201" s="21"/>
-      <c r="H201" s="21"/>
+      <c r="A201" s="22"/>
+      <c r="G201" s="23"/>
+      <c r="H201" s="23"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="20"/>
-      <c r="G202" s="21"/>
-      <c r="H202" s="21"/>
+      <c r="A202" s="22"/>
+      <c r="G202" s="23"/>
+      <c r="H202" s="23"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="20"/>
-      <c r="G203" s="21"/>
-      <c r="H203" s="21"/>
+      <c r="A203" s="22"/>
+      <c r="G203" s="23"/>
+      <c r="H203" s="23"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="20"/>
-      <c r="G204" s="21"/>
-      <c r="H204" s="21"/>
+      <c r="A204" s="22"/>
+      <c r="G204" s="23"/>
+      <c r="H204" s="23"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="20"/>
-      <c r="G205" s="21"/>
-      <c r="H205" s="21"/>
+      <c r="A205" s="22"/>
+      <c r="G205" s="23"/>
+      <c r="H205" s="23"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="20"/>
-      <c r="G206" s="21"/>
-      <c r="H206" s="21"/>
+      <c r="A206" s="22"/>
+      <c r="G206" s="23"/>
+      <c r="H206" s="23"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="20"/>
-      <c r="G207" s="21"/>
-      <c r="H207" s="21"/>
+      <c r="A207" s="22"/>
+      <c r="G207" s="23"/>
+      <c r="H207" s="23"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="20"/>
-      <c r="G208" s="21"/>
-      <c r="H208" s="21"/>
+      <c r="A208" s="22"/>
+      <c r="G208" s="23"/>
+      <c r="H208" s="23"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="20"/>
-      <c r="G209" s="21"/>
-      <c r="H209" s="21"/>
+      <c r="A209" s="22"/>
+      <c r="G209" s="23"/>
+      <c r="H209" s="23"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="20"/>
-      <c r="G210" s="21"/>
-      <c r="H210" s="21"/>
+      <c r="A210" s="22"/>
+      <c r="G210" s="23"/>
+      <c r="H210" s="23"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="20"/>
-      <c r="G211" s="21"/>
-      <c r="H211" s="21"/>
+      <c r="A211" s="22"/>
+      <c r="G211" s="23"/>
+      <c r="H211" s="23"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="20"/>
-      <c r="G212" s="21"/>
-      <c r="H212" s="21"/>
+      <c r="A212" s="22"/>
+      <c r="G212" s="23"/>
+      <c r="H212" s="23"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="20"/>
-      <c r="G213" s="21"/>
-      <c r="H213" s="21"/>
+      <c r="A213" s="22"/>
+      <c r="G213" s="23"/>
+      <c r="H213" s="23"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="20"/>
-      <c r="G214" s="21"/>
-      <c r="H214" s="21"/>
+      <c r="A214" s="22"/>
+      <c r="G214" s="23"/>
+      <c r="H214" s="23"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="20"/>
-      <c r="G215" s="21"/>
-      <c r="H215" s="21"/>
+      <c r="A215" s="22"/>
+      <c r="G215" s="23"/>
+      <c r="H215" s="23"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="20"/>
-      <c r="G216" s="21"/>
-      <c r="H216" s="21"/>
+      <c r="A216" s="22"/>
+      <c r="G216" s="23"/>
+      <c r="H216" s="23"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="20"/>
-      <c r="G217" s="21"/>
-      <c r="H217" s="21"/>
+      <c r="A217" s="22"/>
+      <c r="G217" s="23"/>
+      <c r="H217" s="23"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="20"/>
-      <c r="G218" s="21"/>
-      <c r="H218" s="21"/>
+      <c r="A218" s="22"/>
+      <c r="G218" s="23"/>
+      <c r="H218" s="23"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="20"/>
-      <c r="G219" s="21"/>
-      <c r="H219" s="21"/>
+      <c r="A219" s="22"/>
+      <c r="G219" s="23"/>
+      <c r="H219" s="23"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="20"/>
-      <c r="G220" s="21"/>
-      <c r="H220" s="21"/>
+      <c r="A220" s="22"/>
+      <c r="G220" s="23"/>
+      <c r="H220" s="23"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="20"/>
-      <c r="G221" s="21"/>
-      <c r="H221" s="21"/>
+      <c r="A221" s="22"/>
+      <c r="G221" s="23"/>
+      <c r="H221" s="23"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="20"/>
-      <c r="G222" s="21"/>
-      <c r="H222" s="21"/>
+      <c r="A222" s="22"/>
+      <c r="G222" s="23"/>
+      <c r="H222" s="23"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="20"/>
-      <c r="G223" s="21"/>
-      <c r="H223" s="21"/>
+      <c r="A223" s="22"/>
+      <c r="G223" s="23"/>
+      <c r="H223" s="23"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="20"/>
-      <c r="G224" s="21"/>
-      <c r="H224" s="21"/>
+      <c r="A224" s="22"/>
+      <c r="G224" s="23"/>
+      <c r="H224" s="23"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="20"/>
-      <c r="G225" s="21"/>
-      <c r="H225" s="21"/>
+      <c r="A225" s="22"/>
+      <c r="G225" s="23"/>
+      <c r="H225" s="23"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="20"/>
-      <c r="G226" s="21"/>
-      <c r="H226" s="21"/>
+      <c r="A226" s="22"/>
+      <c r="G226" s="23"/>
+      <c r="H226" s="23"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="20"/>
-      <c r="G227" s="21"/>
-      <c r="H227" s="21"/>
+      <c r="A227" s="22"/>
+      <c r="G227" s="23"/>
+      <c r="H227" s="23"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="20"/>
-      <c r="G228" s="21"/>
-      <c r="H228" s="21"/>
+      <c r="A228" s="22"/>
+      <c r="G228" s="23"/>
+      <c r="H228" s="23"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="20"/>
-      <c r="G229" s="21"/>
-      <c r="H229" s="21"/>
+      <c r="A229" s="22"/>
+      <c r="G229" s="23"/>
+      <c r="H229" s="23"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="20"/>
-      <c r="G230" s="21"/>
-      <c r="H230" s="21"/>
+      <c r="A230" s="22"/>
+      <c r="G230" s="23"/>
+      <c r="H230" s="23"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="20"/>
-      <c r="G231" s="21"/>
-      <c r="H231" s="21"/>
+      <c r="A231" s="22"/>
+      <c r="G231" s="23"/>
+      <c r="H231" s="23"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="20"/>
-      <c r="G232" s="21"/>
-      <c r="H232" s="21"/>
+      <c r="A232" s="22"/>
+      <c r="G232" s="23"/>
+      <c r="H232" s="23"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="20"/>
-      <c r="G233" s="21"/>
-      <c r="H233" s="21"/>
+      <c r="A233" s="22"/>
+      <c r="G233" s="23"/>
+      <c r="H233" s="23"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="20"/>
-      <c r="G234" s="21"/>
-      <c r="H234" s="21"/>
+      <c r="A234" s="22"/>
+      <c r="G234" s="23"/>
+      <c r="H234" s="23"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="20"/>
-      <c r="G235" s="21"/>
-      <c r="H235" s="21"/>
+      <c r="A235" s="22"/>
+      <c r="G235" s="23"/>
+      <c r="H235" s="23"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="20"/>
-      <c r="G236" s="21"/>
-      <c r="H236" s="21"/>
+      <c r="A236" s="22"/>
+      <c r="G236" s="23"/>
+      <c r="H236" s="23"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="20"/>
-      <c r="G237" s="21"/>
-      <c r="H237" s="21"/>
+      <c r="A237" s="22"/>
+      <c r="G237" s="23"/>
+      <c r="H237" s="23"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="20"/>
-      <c r="G238" s="21"/>
-      <c r="H238" s="21"/>
+      <c r="A238" s="22"/>
+      <c r="G238" s="23"/>
+      <c r="H238" s="23"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="20"/>
-      <c r="G239" s="21"/>
-      <c r="H239" s="21"/>
+      <c r="A239" s="22"/>
+      <c r="G239" s="23"/>
+      <c r="H239" s="23"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="20"/>
-      <c r="G240" s="21"/>
-      <c r="H240" s="21"/>
+      <c r="A240" s="22"/>
+      <c r="G240" s="23"/>
+      <c r="H240" s="23"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="20"/>
-      <c r="G241" s="21"/>
-      <c r="H241" s="21"/>
+      <c r="A241" s="22"/>
+      <c r="G241" s="23"/>
+      <c r="H241" s="23"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="20"/>
-      <c r="G242" s="21"/>
-      <c r="H242" s="21"/>
+      <c r="A242" s="22"/>
+      <c r="G242" s="23"/>
+      <c r="H242" s="23"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="20"/>
-      <c r="G243" s="21"/>
-      <c r="H243" s="21"/>
+      <c r="A243" s="22"/>
+      <c r="G243" s="23"/>
+      <c r="H243" s="23"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="20"/>
-      <c r="G244" s="21"/>
-      <c r="H244" s="21"/>
+      <c r="A244" s="22"/>
+      <c r="G244" s="23"/>
+      <c r="H244" s="23"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="20"/>
-      <c r="G245" s="21"/>
-      <c r="H245" s="21"/>
+      <c r="A245" s="22"/>
+      <c r="G245" s="23"/>
+      <c r="H245" s="23"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="20"/>
-      <c r="G246" s="21"/>
-      <c r="H246" s="21"/>
+      <c r="A246" s="22"/>
+      <c r="G246" s="23"/>
+      <c r="H246" s="23"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="20"/>
-      <c r="G247" s="21"/>
-      <c r="H247" s="21"/>
+      <c r="A247" s="22"/>
+      <c r="G247" s="23"/>
+      <c r="H247" s="23"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="20"/>
-      <c r="G248" s="21"/>
-      <c r="H248" s="21"/>
+      <c r="A248" s="22"/>
+      <c r="G248" s="23"/>
+      <c r="H248" s="23"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="20"/>
-      <c r="G249" s="21"/>
-      <c r="H249" s="21"/>
+      <c r="A249" s="22"/>
+      <c r="G249" s="23"/>
+      <c r="H249" s="23"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="20"/>
-      <c r="G250" s="21"/>
-      <c r="H250" s="21"/>
+      <c r="A250" s="22"/>
+      <c r="G250" s="23"/>
+      <c r="H250" s="23"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="20"/>
-      <c r="G251" s="21"/>
-      <c r="H251" s="21"/>
+      <c r="A251" s="22"/>
+      <c r="G251" s="23"/>
+      <c r="H251" s="23"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="20"/>
-      <c r="G252" s="21"/>
-      <c r="H252" s="21"/>
+      <c r="A252" s="22"/>
+      <c r="G252" s="23"/>
+      <c r="H252" s="23"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="20"/>
-      <c r="G253" s="21"/>
-      <c r="H253" s="21"/>
+      <c r="A253" s="22"/>
+      <c r="G253" s="23"/>
+      <c r="H253" s="23"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="20"/>
-      <c r="G254" s="21"/>
-      <c r="H254" s="21"/>
+      <c r="A254" s="22"/>
+      <c r="G254" s="23"/>
+      <c r="H254" s="23"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="20"/>
-      <c r="G255" s="21"/>
-      <c r="H255" s="21"/>
+      <c r="A255" s="22"/>
+      <c r="G255" s="23"/>
+      <c r="H255" s="23"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="20"/>
-      <c r="G256" s="21"/>
-      <c r="H256" s="21"/>
+      <c r="A256" s="22"/>
+      <c r="G256" s="23"/>
+      <c r="H256" s="23"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="20"/>
-      <c r="G257" s="21"/>
-      <c r="H257" s="21"/>
+      <c r="A257" s="22"/>
+      <c r="G257" s="23"/>
+      <c r="H257" s="23"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="20"/>
-      <c r="G258" s="21"/>
-      <c r="H258" s="21"/>
+      <c r="A258" s="22"/>
+      <c r="G258" s="23"/>
+      <c r="H258" s="23"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="20"/>
-      <c r="G259" s="21"/>
-      <c r="H259" s="21"/>
+      <c r="A259" s="22"/>
+      <c r="G259" s="23"/>
+      <c r="H259" s="23"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="20"/>
-      <c r="G260" s="21"/>
-      <c r="H260" s="21"/>
+      <c r="A260" s="22"/>
+      <c r="G260" s="23"/>
+      <c r="H260" s="23"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="20"/>
-      <c r="G261" s="21"/>
-      <c r="H261" s="21"/>
+      <c r="A261" s="22"/>
+      <c r="G261" s="23"/>
+      <c r="H261" s="23"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="20"/>
-      <c r="G262" s="21"/>
-      <c r="H262" s="21"/>
+      <c r="A262" s="22"/>
+      <c r="G262" s="23"/>
+      <c r="H262" s="23"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="20"/>
-      <c r="G263" s="21"/>
-      <c r="H263" s="21"/>
+      <c r="A263" s="22"/>
+      <c r="G263" s="23"/>
+      <c r="H263" s="23"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="20"/>
-      <c r="G264" s="21"/>
-      <c r="H264" s="21"/>
+      <c r="A264" s="22"/>
+      <c r="G264" s="23"/>
+      <c r="H264" s="23"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="20"/>
-      <c r="G265" s="21"/>
-      <c r="H265" s="21"/>
+      <c r="A265" s="22"/>
+      <c r="G265" s="23"/>
+      <c r="H265" s="23"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="20"/>
-      <c r="G266" s="21"/>
-      <c r="H266" s="21"/>
+      <c r="A266" s="22"/>
+      <c r="G266" s="23"/>
+      <c r="H266" s="23"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="20"/>
-      <c r="G267" s="21"/>
-      <c r="H267" s="21"/>
+      <c r="A267" s="22"/>
+      <c r="G267" s="23"/>
+      <c r="H267" s="23"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="20"/>
-      <c r="G268" s="21"/>
-      <c r="H268" s="21"/>
+      <c r="A268" s="22"/>
+      <c r="G268" s="23"/>
+      <c r="H268" s="23"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="20"/>
-      <c r="G269" s="21"/>
-      <c r="H269" s="21"/>
+      <c r="A269" s="22"/>
+      <c r="G269" s="23"/>
+      <c r="H269" s="23"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="20"/>
-      <c r="G270" s="21"/>
-      <c r="H270" s="21"/>
+      <c r="A270" s="22"/>
+      <c r="G270" s="23"/>
+      <c r="H270" s="23"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="20"/>
-      <c r="G271" s="21"/>
-      <c r="H271" s="21"/>
+      <c r="A271" s="22"/>
+      <c r="G271" s="23"/>
+      <c r="H271" s="23"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="20"/>
-      <c r="G272" s="21"/>
-      <c r="H272" s="21"/>
+      <c r="A272" s="22"/>
+      <c r="G272" s="23"/>
+      <c r="H272" s="23"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="20"/>
-      <c r="G273" s="21"/>
-      <c r="H273" s="21"/>
+      <c r="A273" s="22"/>
+      <c r="G273" s="23"/>
+      <c r="H273" s="23"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="20"/>
-      <c r="G274" s="21"/>
-      <c r="H274" s="21"/>
+      <c r="A274" s="22"/>
+      <c r="G274" s="23"/>
+      <c r="H274" s="23"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="20"/>
-      <c r="G275" s="21"/>
-      <c r="H275" s="21"/>
+      <c r="A275" s="22"/>
+      <c r="G275" s="23"/>
+      <c r="H275" s="23"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="20"/>
-      <c r="G276" s="21"/>
-      <c r="H276" s="21"/>
+      <c r="A276" s="22"/>
+      <c r="G276" s="23"/>
+      <c r="H276" s="23"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="20"/>
-      <c r="G277" s="21"/>
-      <c r="H277" s="21"/>
+      <c r="A277" s="22"/>
+      <c r="G277" s="23"/>
+      <c r="H277" s="23"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="20"/>
-      <c r="G278" s="21"/>
-      <c r="H278" s="21"/>
+      <c r="A278" s="22"/>
+      <c r="G278" s="23"/>
+      <c r="H278" s="23"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="20"/>
-      <c r="G279" s="21"/>
-      <c r="H279" s="21"/>
+      <c r="A279" s="22"/>
+      <c r="G279" s="23"/>
+      <c r="H279" s="23"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="20"/>
-      <c r="G280" s="21"/>
-      <c r="H280" s="21"/>
+      <c r="A280" s="22"/>
+      <c r="G280" s="23"/>
+      <c r="H280" s="23"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="20"/>
-      <c r="G281" s="21"/>
-      <c r="H281" s="21"/>
+      <c r="A281" s="22"/>
+      <c r="G281" s="23"/>
+      <c r="H281" s="23"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="20"/>
-      <c r="G282" s="21"/>
-      <c r="H282" s="21"/>
+      <c r="A282" s="22"/>
+      <c r="G282" s="23"/>
+      <c r="H282" s="23"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="20"/>
-      <c r="G283" s="21"/>
-      <c r="H283" s="21"/>
+      <c r="A283" s="22"/>
+      <c r="G283" s="23"/>
+      <c r="H283" s="23"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="20"/>
-      <c r="G284" s="21"/>
-      <c r="H284" s="21"/>
+      <c r="A284" s="22"/>
+      <c r="G284" s="23"/>
+      <c r="H284" s="23"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="20"/>
-      <c r="G285" s="21"/>
-      <c r="H285" s="21"/>
+      <c r="A285" s="22"/>
+      <c r="G285" s="23"/>
+      <c r="H285" s="23"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="20"/>
-      <c r="G286" s="21"/>
-      <c r="H286" s="21"/>
+      <c r="A286" s="22"/>
+      <c r="G286" s="23"/>
+      <c r="H286" s="23"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="20"/>
-      <c r="G287" s="21"/>
-      <c r="H287" s="21"/>
+      <c r="A287" s="22"/>
+      <c r="G287" s="23"/>
+      <c r="H287" s="23"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="20"/>
-      <c r="G288" s="21"/>
-      <c r="H288" s="21"/>
+      <c r="A288" s="22"/>
+      <c r="G288" s="23"/>
+      <c r="H288" s="23"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="20"/>
-      <c r="G289" s="21"/>
-      <c r="H289" s="21"/>
+      <c r="A289" s="22"/>
+      <c r="G289" s="23"/>
+      <c r="H289" s="23"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="20"/>
-      <c r="G290" s="21"/>
-      <c r="H290" s="21"/>
+      <c r="A290" s="22"/>
+      <c r="G290" s="23"/>
+      <c r="H290" s="23"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="20"/>
-      <c r="G291" s="21"/>
-      <c r="H291" s="21"/>
+      <c r="A291" s="22"/>
+      <c r="G291" s="23"/>
+      <c r="H291" s="23"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="20"/>
-      <c r="G292" s="21"/>
-      <c r="H292" s="21"/>
+      <c r="A292" s="22"/>
+      <c r="G292" s="23"/>
+      <c r="H292" s="23"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="20"/>
-      <c r="G293" s="21"/>
-      <c r="H293" s="21"/>
+      <c r="A293" s="22"/>
+      <c r="G293" s="23"/>
+      <c r="H293" s="23"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="20"/>
-      <c r="G294" s="21"/>
-      <c r="H294" s="21"/>
+      <c r="A294" s="22"/>
+      <c r="G294" s="23"/>
+      <c r="H294" s="23"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="20"/>
-      <c r="G295" s="21"/>
-      <c r="H295" s="21"/>
+      <c r="A295" s="22"/>
+      <c r="G295" s="23"/>
+      <c r="H295" s="23"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="20"/>
-      <c r="G296" s="21"/>
-      <c r="H296" s="21"/>
+      <c r="A296" s="22"/>
+      <c r="G296" s="23"/>
+      <c r="H296" s="23"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="20"/>
-      <c r="G297" s="21"/>
-      <c r="H297" s="21"/>
+      <c r="A297" s="22"/>
+      <c r="G297" s="23"/>
+      <c r="H297" s="23"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="20"/>
-      <c r="G298" s="21"/>
-      <c r="H298" s="21"/>
+      <c r="A298" s="22"/>
+      <c r="G298" s="23"/>
+      <c r="H298" s="23"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="20"/>
-      <c r="G299" s="21"/>
-      <c r="H299" s="21"/>
+      <c r="A299" s="22"/>
+      <c r="G299" s="23"/>
+      <c r="H299" s="23"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="20"/>
-      <c r="G300" s="21"/>
-      <c r="H300" s="21"/>
+      <c r="A300" s="22"/>
+      <c r="G300" s="23"/>
+      <c r="H300" s="23"/>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="20"/>
-      <c r="G301" s="21"/>
-      <c r="H301" s="21"/>
+      <c r="A301" s="22"/>
+      <c r="G301" s="23"/>
+      <c r="H301" s="23"/>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="20"/>
-      <c r="G302" s="21"/>
-      <c r="H302" s="21"/>
+      <c r="A302" s="22"/>
+      <c r="G302" s="23"/>
+      <c r="H302" s="23"/>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="20"/>
-      <c r="G303" s="21"/>
-      <c r="H303" s="21"/>
+      <c r="A303" s="22"/>
+      <c r="G303" s="23"/>
+      <c r="H303" s="23"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="20"/>
-      <c r="G304" s="21"/>
-      <c r="H304" s="21"/>
+      <c r="A304" s="22"/>
+      <c r="G304" s="23"/>
+      <c r="H304" s="23"/>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="20"/>
-      <c r="G305" s="21"/>
-      <c r="H305" s="21"/>
+      <c r="A305" s="22"/>
+      <c r="G305" s="23"/>
+      <c r="H305" s="23"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="20"/>
-      <c r="G306" s="21"/>
-      <c r="H306" s="21"/>
+      <c r="A306" s="22"/>
+      <c r="G306" s="23"/>
+      <c r="H306" s="23"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="20"/>
-      <c r="G307" s="21"/>
-      <c r="H307" s="21"/>
+      <c r="A307" s="22"/>
+      <c r="G307" s="23"/>
+      <c r="H307" s="23"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="20"/>
-      <c r="G308" s="21"/>
-      <c r="H308" s="21"/>
+      <c r="A308" s="22"/>
+      <c r="G308" s="23"/>
+      <c r="H308" s="23"/>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="20"/>
-      <c r="G309" s="21"/>
-      <c r="H309" s="21"/>
+      <c r="A309" s="22"/>
+      <c r="G309" s="23"/>
+      <c r="H309" s="23"/>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="20"/>
-      <c r="G310" s="21"/>
-      <c r="H310" s="21"/>
+      <c r="A310" s="22"/>
+      <c r="G310" s="23"/>
+      <c r="H310" s="23"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="20"/>
-      <c r="G311" s="21"/>
-      <c r="H311" s="21"/>
+      <c r="A311" s="22"/>
+      <c r="G311" s="23"/>
+      <c r="H311" s="23"/>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="20"/>
-      <c r="G312" s="21"/>
-      <c r="H312" s="21"/>
+      <c r="A312" s="22"/>
+      <c r="G312" s="23"/>
+      <c r="H312" s="23"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="20"/>
-      <c r="G313" s="21"/>
-      <c r="H313" s="21"/>
+      <c r="A313" s="22"/>
+      <c r="G313" s="23"/>
+      <c r="H313" s="23"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="20"/>
-      <c r="G314" s="21"/>
-      <c r="H314" s="21"/>
+      <c r="A314" s="22"/>
+      <c r="G314" s="23"/>
+      <c r="H314" s="23"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="20"/>
-      <c r="G315" s="21"/>
-      <c r="H315" s="21"/>
+      <c r="A315" s="22"/>
+      <c r="G315" s="23"/>
+      <c r="H315" s="23"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="20"/>
-      <c r="G316" s="21"/>
-      <c r="H316" s="21"/>
+      <c r="A316" s="22"/>
+      <c r="G316" s="23"/>
+      <c r="H316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="20"/>
-      <c r="G317" s="21"/>
-      <c r="H317" s="21"/>
+      <c r="A317" s="22"/>
+      <c r="G317" s="23"/>
+      <c r="H317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="20"/>
-      <c r="G318" s="21"/>
-      <c r="H318" s="21"/>
+      <c r="A318" s="22"/>
+      <c r="G318" s="23"/>
+      <c r="H318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="20"/>
-      <c r="G319" s="21"/>
-      <c r="H319" s="21"/>
+      <c r="A319" s="22"/>
+      <c r="G319" s="23"/>
+      <c r="H319" s="23"/>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="20"/>
-      <c r="G320" s="21"/>
-      <c r="H320" s="21"/>
+      <c r="A320" s="22"/>
+      <c r="G320" s="23"/>
+      <c r="H320" s="23"/>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="20"/>
-      <c r="G321" s="21"/>
-      <c r="H321" s="21"/>
+      <c r="A321" s="22"/>
+      <c r="G321" s="23"/>
+      <c r="H321" s="23"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="20"/>
-      <c r="G322" s="21"/>
-      <c r="H322" s="21"/>
+      <c r="A322" s="22"/>
+      <c r="G322" s="23"/>
+      <c r="H322" s="23"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="20"/>
-      <c r="G323" s="21"/>
-      <c r="H323" s="21"/>
+      <c r="A323" s="22"/>
+      <c r="G323" s="23"/>
+      <c r="H323" s="23"/>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="20"/>
-      <c r="G324" s="21"/>
-      <c r="H324" s="21"/>
+      <c r="A324" s="22"/>
+      <c r="G324" s="23"/>
+      <c r="H324" s="23"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="20"/>
-      <c r="G325" s="21"/>
-      <c r="H325" s="21"/>
+      <c r="A325" s="22"/>
+      <c r="G325" s="23"/>
+      <c r="H325" s="23"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="20"/>
-      <c r="G326" s="21"/>
-      <c r="H326" s="21"/>
+      <c r="A326" s="22"/>
+      <c r="G326" s="23"/>
+      <c r="H326" s="23"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="20"/>
-      <c r="G327" s="21"/>
-      <c r="H327" s="21"/>
+      <c r="A327" s="22"/>
+      <c r="G327" s="23"/>
+      <c r="H327" s="23"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="20"/>
-      <c r="G328" s="21"/>
-      <c r="H328" s="21"/>
+      <c r="A328" s="22"/>
+      <c r="G328" s="23"/>
+      <c r="H328" s="23"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="20"/>
-      <c r="G329" s="21"/>
-      <c r="H329" s="21"/>
+      <c r="A329" s="22"/>
+      <c r="G329" s="23"/>
+      <c r="H329" s="23"/>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="20"/>
-      <c r="G330" s="21"/>
-      <c r="H330" s="21"/>
+      <c r="A330" s="22"/>
+      <c r="G330" s="23"/>
+      <c r="H330" s="23"/>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="20"/>
-      <c r="G331" s="21"/>
-      <c r="H331" s="21"/>
+      <c r="A331" s="22"/>
+      <c r="G331" s="23"/>
+      <c r="H331" s="23"/>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="20"/>
-      <c r="G332" s="21"/>
-      <c r="H332" s="21"/>
+      <c r="A332" s="22"/>
+      <c r="G332" s="23"/>
+      <c r="H332" s="23"/>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="20"/>
-      <c r="G333" s="21"/>
-      <c r="H333" s="21"/>
+      <c r="A333" s="22"/>
+      <c r="G333" s="23"/>
+      <c r="H333" s="23"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="20"/>
-      <c r="G334" s="21"/>
-      <c r="H334" s="21"/>
+      <c r="A334" s="22"/>
+      <c r="G334" s="23"/>
+      <c r="H334" s="23"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="20"/>
-      <c r="G335" s="21"/>
-      <c r="H335" s="21"/>
+      <c r="A335" s="22"/>
+      <c r="G335" s="23"/>
+      <c r="H335" s="23"/>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="20"/>
-      <c r="G336" s="21"/>
-      <c r="H336" s="21"/>
+      <c r="A336" s="22"/>
+      <c r="G336" s="23"/>
+      <c r="H336" s="23"/>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="20"/>
-      <c r="G337" s="21"/>
-      <c r="H337" s="21"/>
+      <c r="A337" s="22"/>
+      <c r="G337" s="23"/>
+      <c r="H337" s="23"/>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="20"/>
-      <c r="G338" s="21"/>
-      <c r="H338" s="21"/>
+      <c r="A338" s="22"/>
+      <c r="G338" s="23"/>
+      <c r="H338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="20"/>
-      <c r="G339" s="21"/>
-      <c r="H339" s="21"/>
+      <c r="A339" s="22"/>
+      <c r="G339" s="23"/>
+      <c r="H339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="20"/>
-      <c r="G340" s="21"/>
-      <c r="H340" s="21"/>
+      <c r="A340" s="22"/>
+      <c r="G340" s="23"/>
+      <c r="H340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="20"/>
-      <c r="G341" s="21"/>
-      <c r="H341" s="21"/>
+      <c r="A341" s="22"/>
+      <c r="G341" s="23"/>
+      <c r="H341" s="23"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="20"/>
-      <c r="G342" s="21"/>
-      <c r="H342" s="21"/>
+      <c r="A342" s="22"/>
+      <c r="G342" s="23"/>
+      <c r="H342" s="23"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="20"/>
-      <c r="G343" s="21"/>
-      <c r="H343" s="21"/>
+      <c r="A343" s="22"/>
+      <c r="G343" s="23"/>
+      <c r="H343" s="23"/>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="20"/>
-      <c r="G344" s="21"/>
-      <c r="H344" s="21"/>
+      <c r="A344" s="22"/>
+      <c r="G344" s="23"/>
+      <c r="H344" s="23"/>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="20"/>
-      <c r="G345" s="21"/>
-      <c r="H345" s="21"/>
+      <c r="A345" s="22"/>
+      <c r="G345" s="23"/>
+      <c r="H345" s="23"/>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="20"/>
-      <c r="G346" s="21"/>
-      <c r="H346" s="21"/>
+      <c r="A346" s="22"/>
+      <c r="G346" s="23"/>
+      <c r="H346" s="23"/>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="20"/>
-      <c r="G347" s="21"/>
-      <c r="H347" s="21"/>
+      <c r="A347" s="22"/>
+      <c r="G347" s="23"/>
+      <c r="H347" s="23"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="20"/>
-      <c r="G348" s="21"/>
-      <c r="H348" s="21"/>
+      <c r="A348" s="22"/>
+      <c r="G348" s="23"/>
+      <c r="H348" s="23"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="20"/>
-      <c r="G349" s="21"/>
-      <c r="H349" s="21"/>
+      <c r="A349" s="22"/>
+      <c r="G349" s="23"/>
+      <c r="H349" s="23"/>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="20"/>
-      <c r="G350" s="21"/>
-      <c r="H350" s="21"/>
+      <c r="A350" s="22"/>
+      <c r="G350" s="23"/>
+      <c r="H350" s="23"/>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="20"/>
-      <c r="G351" s="21"/>
-      <c r="H351" s="21"/>
+      <c r="A351" s="22"/>
+      <c r="G351" s="23"/>
+      <c r="H351" s="23"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="20"/>
-      <c r="G352" s="21"/>
-      <c r="H352" s="21"/>
+      <c r="A352" s="22"/>
+      <c r="G352" s="23"/>
+      <c r="H352" s="23"/>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="20"/>
-      <c r="G353" s="21"/>
-      <c r="H353" s="21"/>
+      <c r="A353" s="22"/>
+      <c r="G353" s="23"/>
+      <c r="H353" s="23"/>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="20"/>
-      <c r="G354" s="21"/>
-      <c r="H354" s="21"/>
+      <c r="A354" s="22"/>
+      <c r="G354" s="23"/>
+      <c r="H354" s="23"/>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="20"/>
-      <c r="G355" s="21"/>
-      <c r="H355" s="21"/>
+      <c r="A355" s="22"/>
+      <c r="G355" s="23"/>
+      <c r="H355" s="23"/>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="20"/>
-      <c r="G356" s="21"/>
-      <c r="H356" s="21"/>
+      <c r="A356" s="22"/>
+      <c r="G356" s="23"/>
+      <c r="H356" s="23"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="20"/>
-      <c r="G357" s="21"/>
-      <c r="H357" s="21"/>
+      <c r="A357" s="22"/>
+      <c r="G357" s="23"/>
+      <c r="H357" s="23"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="20"/>
-      <c r="G358" s="21"/>
-      <c r="H358" s="21"/>
+      <c r="A358" s="22"/>
+      <c r="G358" s="23"/>
+      <c r="H358" s="23"/>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="20"/>
-      <c r="G359" s="21"/>
-      <c r="H359" s="21"/>
+      <c r="A359" s="22"/>
+      <c r="G359" s="23"/>
+      <c r="H359" s="23"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="20"/>
-      <c r="G360" s="21"/>
-      <c r="H360" s="21"/>
+      <c r="A360" s="22"/>
+      <c r="G360" s="23"/>
+      <c r="H360" s="23"/>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="20"/>
-      <c r="G361" s="21"/>
-      <c r="H361" s="21"/>
+      <c r="A361" s="22"/>
+      <c r="G361" s="23"/>
+      <c r="H361" s="23"/>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="20"/>
-      <c r="G362" s="21"/>
-      <c r="H362" s="21"/>
+      <c r="A362" s="22"/>
+      <c r="G362" s="23"/>
+      <c r="H362" s="23"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="20"/>
-      <c r="G363" s="21"/>
-      <c r="H363" s="21"/>
+      <c r="A363" s="22"/>
+      <c r="G363" s="23"/>
+      <c r="H363" s="23"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="20"/>
-      <c r="G364" s="21"/>
-      <c r="H364" s="21"/>
+      <c r="A364" s="22"/>
+      <c r="G364" s="23"/>
+      <c r="H364" s="23"/>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="20"/>
-      <c r="G365" s="21"/>
-      <c r="H365" s="21"/>
+      <c r="A365" s="22"/>
+      <c r="G365" s="23"/>
+      <c r="H365" s="23"/>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="20"/>
-      <c r="G366" s="21"/>
-      <c r="H366" s="21"/>
+      <c r="A366" s="22"/>
+      <c r="G366" s="23"/>
+      <c r="H366" s="23"/>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="20"/>
-      <c r="G367" s="21"/>
-      <c r="H367" s="21"/>
+      <c r="A367" s="22"/>
+      <c r="G367" s="23"/>
+      <c r="H367" s="23"/>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="20"/>
-      <c r="G368" s="21"/>
-      <c r="H368" s="21"/>
+      <c r="A368" s="22"/>
+      <c r="G368" s="23"/>
+      <c r="H368" s="23"/>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="20"/>
-      <c r="G369" s="21"/>
-      <c r="H369" s="21"/>
+      <c r="A369" s="22"/>
+      <c r="G369" s="23"/>
+      <c r="H369" s="23"/>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="20"/>
-      <c r="G370" s="21"/>
-      <c r="H370" s="21"/>
+      <c r="A370" s="22"/>
+      <c r="G370" s="23"/>
+      <c r="H370" s="23"/>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="20"/>
-      <c r="G371" s="21"/>
-      <c r="H371" s="21"/>
+      <c r="A371" s="22"/>
+      <c r="G371" s="23"/>
+      <c r="H371" s="23"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="20"/>
-      <c r="G372" s="21"/>
-      <c r="H372" s="21"/>
+      <c r="A372" s="22"/>
+      <c r="G372" s="23"/>
+      <c r="H372" s="23"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="20"/>
-      <c r="G373" s="21"/>
-      <c r="H373" s="21"/>
+      <c r="A373" s="22"/>
+      <c r="G373" s="23"/>
+      <c r="H373" s="23"/>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="20"/>
-      <c r="G374" s="21"/>
-      <c r="H374" s="21"/>
+      <c r="A374" s="22"/>
+      <c r="G374" s="23"/>
+      <c r="H374" s="23"/>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="20"/>
-      <c r="G375" s="21"/>
-      <c r="H375" s="21"/>
+      <c r="A375" s="22"/>
+      <c r="G375" s="23"/>
+      <c r="H375" s="23"/>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="20"/>
-      <c r="G376" s="21"/>
-      <c r="H376" s="21"/>
+      <c r="A376" s="22"/>
+      <c r="G376" s="23"/>
+      <c r="H376" s="23"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="20"/>
-      <c r="G377" s="21"/>
-      <c r="H377" s="21"/>
+      <c r="A377" s="22"/>
+      <c r="G377" s="23"/>
+      <c r="H377" s="23"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="20"/>
-      <c r="G378" s="21"/>
-      <c r="H378" s="21"/>
+      <c r="A378" s="22"/>
+      <c r="G378" s="23"/>
+      <c r="H378" s="23"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="20"/>
-      <c r="G379" s="21"/>
-      <c r="H379" s="21"/>
+      <c r="A379" s="22"/>
+      <c r="G379" s="23"/>
+      <c r="H379" s="23"/>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="20"/>
-      <c r="G380" s="21"/>
-      <c r="H380" s="21"/>
+      <c r="A380" s="22"/>
+      <c r="G380" s="23"/>
+      <c r="H380" s="23"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="20"/>
-      <c r="G381" s="21"/>
-      <c r="H381" s="21"/>
+      <c r="A381" s="22"/>
+      <c r="G381" s="23"/>
+      <c r="H381" s="23"/>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="20"/>
-      <c r="G382" s="21"/>
-      <c r="H382" s="21"/>
+      <c r="A382" s="22"/>
+      <c r="G382" s="23"/>
+      <c r="H382" s="23"/>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="20"/>
-      <c r="G383" s="21"/>
-      <c r="H383" s="21"/>
+      <c r="A383" s="22"/>
+      <c r="G383" s="23"/>
+      <c r="H383" s="23"/>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="20"/>
-      <c r="G384" s="21"/>
-      <c r="H384" s="21"/>
+      <c r="A384" s="22"/>
+      <c r="G384" s="23"/>
+      <c r="H384" s="23"/>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="20"/>
-      <c r="G385" s="21"/>
-      <c r="H385" s="21"/>
+      <c r="A385" s="22"/>
+      <c r="G385" s="23"/>
+      <c r="H385" s="23"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="20"/>
-      <c r="G386" s="21"/>
-      <c r="H386" s="21"/>
+      <c r="A386" s="22"/>
+      <c r="G386" s="23"/>
+      <c r="H386" s="23"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="20"/>
-      <c r="G387" s="21"/>
-      <c r="H387" s="21"/>
+      <c r="A387" s="22"/>
+      <c r="G387" s="23"/>
+      <c r="H387" s="23"/>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="20"/>
-      <c r="G388" s="21"/>
-      <c r="H388" s="21"/>
+      <c r="A388" s="22"/>
+      <c r="G388" s="23"/>
+      <c r="H388" s="23"/>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="20"/>
-      <c r="G389" s="21"/>
-      <c r="H389" s="21"/>
+      <c r="A389" s="22"/>
+      <c r="G389" s="23"/>
+      <c r="H389" s="23"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="20"/>
-      <c r="G390" s="21"/>
-      <c r="H390" s="21"/>
+      <c r="A390" s="22"/>
+      <c r="G390" s="23"/>
+      <c r="H390" s="23"/>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="20"/>
-      <c r="G391" s="21"/>
-      <c r="H391" s="21"/>
+      <c r="A391" s="22"/>
+      <c r="G391" s="23"/>
+      <c r="H391" s="23"/>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="20"/>
-      <c r="G392" s="21"/>
-      <c r="H392" s="21"/>
+      <c r="A392" s="22"/>
+      <c r="G392" s="23"/>
+      <c r="H392" s="23"/>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="20"/>
-      <c r="G393" s="21"/>
-      <c r="H393" s="21"/>
+      <c r="A393" s="22"/>
+      <c r="G393" s="23"/>
+      <c r="H393" s="23"/>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="20"/>
-      <c r="G394" s="21"/>
-      <c r="H394" s="21"/>
+      <c r="A394" s="22"/>
+      <c r="G394" s="23"/>
+      <c r="H394" s="23"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="20"/>
-      <c r="G395" s="21"/>
-      <c r="H395" s="21"/>
+      <c r="A395" s="22"/>
+      <c r="G395" s="23"/>
+      <c r="H395" s="23"/>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="20"/>
-      <c r="G396" s="21"/>
-      <c r="H396" s="21"/>
+      <c r="A396" s="22"/>
+      <c r="G396" s="23"/>
+      <c r="H396" s="23"/>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="20"/>
-      <c r="G397" s="21"/>
-      <c r="H397" s="21"/>
+      <c r="A397" s="22"/>
+      <c r="G397" s="23"/>
+      <c r="H397" s="23"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="20"/>
-      <c r="G398" s="21"/>
-      <c r="H398" s="21"/>
+      <c r="A398" s="22"/>
+      <c r="G398" s="23"/>
+      <c r="H398" s="23"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="20"/>
-      <c r="G399" s="21"/>
-      <c r="H399" s="21"/>
+      <c r="A399" s="22"/>
+      <c r="G399" s="23"/>
+      <c r="H399" s="23"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="20"/>
-      <c r="G400" s="21"/>
-      <c r="H400" s="21"/>
+      <c r="A400" s="22"/>
+      <c r="G400" s="23"/>
+      <c r="H400" s="23"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="20"/>
-      <c r="G401" s="21"/>
-      <c r="H401" s="21"/>
+      <c r="A401" s="22"/>
+      <c r="G401" s="23"/>
+      <c r="H401" s="23"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="20"/>
-      <c r="G402" s="21"/>
-      <c r="H402" s="21"/>
+      <c r="A402" s="22"/>
+      <c r="G402" s="23"/>
+      <c r="H402" s="23"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="20"/>
-      <c r="G403" s="21"/>
-      <c r="H403" s="21"/>
+      <c r="A403" s="22"/>
+      <c r="G403" s="23"/>
+      <c r="H403" s="23"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="20"/>
-      <c r="G404" s="21"/>
-      <c r="H404" s="21"/>
+      <c r="A404" s="22"/>
+      <c r="G404" s="23"/>
+      <c r="H404" s="23"/>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A405" s="20"/>
-      <c r="G405" s="21"/>
-      <c r="H405" s="21"/>
+      <c r="A405" s="22"/>
+      <c r="G405" s="23"/>
+      <c r="H405" s="23"/>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A406" s="20"/>
-      <c r="G406" s="21"/>
-      <c r="H406" s="21"/>
+      <c r="A406" s="22"/>
+      <c r="G406" s="23"/>
+      <c r="H406" s="23"/>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A407" s="20"/>
-      <c r="G407" s="21"/>
-      <c r="H407" s="21"/>
+      <c r="A407" s="22"/>
+      <c r="G407" s="23"/>
+      <c r="H407" s="23"/>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="20"/>
-      <c r="G408" s="21"/>
-      <c r="H408" s="21"/>
+      <c r="A408" s="22"/>
+      <c r="G408" s="23"/>
+      <c r="H408" s="23"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="20"/>
-      <c r="G409" s="21"/>
-      <c r="H409" s="21"/>
+      <c r="A409" s="22"/>
+      <c r="G409" s="23"/>
+      <c r="H409" s="23"/>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A410" s="20"/>
-      <c r="G410" s="21"/>
-      <c r="H410" s="21"/>
+      <c r="A410" s="22"/>
+      <c r="G410" s="23"/>
+      <c r="H410" s="23"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A411" s="20"/>
-      <c r="G411" s="21"/>
-      <c r="H411" s="21"/>
+      <c r="A411" s="22"/>
+      <c r="G411" s="23"/>
+      <c r="H411" s="23"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A412" s="20"/>
-      <c r="G412" s="21"/>
-      <c r="H412" s="21"/>
+      <c r="A412" s="22"/>
+      <c r="G412" s="23"/>
+      <c r="H412" s="23"/>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A413" s="20"/>
-      <c r="G413" s="21"/>
-      <c r="H413" s="21"/>
+      <c r="A413" s="22"/>
+      <c r="G413" s="23"/>
+      <c r="H413" s="23"/>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A414" s="20"/>
-      <c r="G414" s="21"/>
-      <c r="H414" s="21"/>
+      <c r="A414" s="22"/>
+      <c r="G414" s="23"/>
+      <c r="H414" s="23"/>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A415" s="20"/>
-      <c r="G415" s="21"/>
-      <c r="H415" s="21"/>
+      <c r="A415" s="22"/>
+      <c r="G415" s="23"/>
+      <c r="H415" s="23"/>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A416" s="20"/>
-      <c r="G416" s="21"/>
-      <c r="H416" s="21"/>
+      <c r="A416" s="22"/>
+      <c r="G416" s="23"/>
+      <c r="H416" s="23"/>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="20"/>
-      <c r="G417" s="21"/>
-      <c r="H417" s="21"/>
+      <c r="A417" s="22"/>
+      <c r="G417" s="23"/>
+      <c r="H417" s="23"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="20"/>
-      <c r="G418" s="21"/>
-      <c r="H418" s="21"/>
+      <c r="A418" s="22"/>
+      <c r="G418" s="23"/>
+      <c r="H418" s="23"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="20"/>
-      <c r="G419" s="21"/>
-      <c r="H419" s="21"/>
+      <c r="A419" s="22"/>
+      <c r="G419" s="23"/>
+      <c r="H419" s="23"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="20"/>
-      <c r="G420" s="21"/>
-      <c r="H420" s="21"/>
+      <c r="A420" s="22"/>
+      <c r="G420" s="23"/>
+      <c r="H420" s="23"/>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="20"/>
-      <c r="G421" s="21"/>
-      <c r="H421" s="21"/>
+      <c r="A421" s="22"/>
+      <c r="G421" s="23"/>
+      <c r="H421" s="23"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="20"/>
-      <c r="G422" s="21"/>
-      <c r="H422" s="21"/>
+      <c r="A422" s="22"/>
+      <c r="G422" s="23"/>
+      <c r="H422" s="23"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="20"/>
-      <c r="G423" s="21"/>
-      <c r="H423" s="21"/>
+      <c r="A423" s="22"/>
+      <c r="G423" s="23"/>
+      <c r="H423" s="23"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="20"/>
-      <c r="G424" s="21"/>
-      <c r="H424" s="21"/>
+      <c r="A424" s="22"/>
+      <c r="G424" s="23"/>
+      <c r="H424" s="23"/>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="20"/>
-      <c r="G425" s="21"/>
-      <c r="H425" s="21"/>
+      <c r="A425" s="22"/>
+      <c r="G425" s="23"/>
+      <c r="H425" s="23"/>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="20"/>
-      <c r="G426" s="21"/>
-      <c r="H426" s="21"/>
+      <c r="A426" s="22"/>
+      <c r="G426" s="23"/>
+      <c r="H426" s="23"/>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="20"/>
-      <c r="G427" s="21"/>
-      <c r="H427" s="21"/>
+      <c r="A427" s="22"/>
+      <c r="G427" s="23"/>
+      <c r="H427" s="23"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="20"/>
-      <c r="G428" s="21"/>
-      <c r="H428" s="21"/>
+      <c r="A428" s="22"/>
+      <c r="G428" s="23"/>
+      <c r="H428" s="23"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="20"/>
-      <c r="G429" s="21"/>
-      <c r="H429" s="21"/>
+      <c r="A429" s="22"/>
+      <c r="G429" s="23"/>
+      <c r="H429" s="23"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="20"/>
-      <c r="G430" s="21"/>
-      <c r="H430" s="21"/>
+      <c r="A430" s="22"/>
+      <c r="G430" s="23"/>
+      <c r="H430" s="23"/>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A431" s="20"/>
-      <c r="G431" s="21"/>
-      <c r="H431" s="21"/>
+      <c r="A431" s="22"/>
+      <c r="G431" s="23"/>
+      <c r="H431" s="23"/>
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="20"/>
-      <c r="G432" s="21"/>
-      <c r="H432" s="21"/>
+      <c r="A432" s="22"/>
+      <c r="G432" s="23"/>
+      <c r="H432" s="23"/>
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="20"/>
-      <c r="G433" s="21"/>
-      <c r="H433" s="21"/>
+      <c r="A433" s="22"/>
+      <c r="G433" s="23"/>
+      <c r="H433" s="23"/>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A434" s="20"/>
-      <c r="G434" s="21"/>
-      <c r="H434" s="21"/>
+      <c r="A434" s="22"/>
+      <c r="G434" s="23"/>
+      <c r="H434" s="23"/>
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="20"/>
-      <c r="G435" s="21"/>
-      <c r="H435" s="21"/>
+      <c r="A435" s="22"/>
+      <c r="G435" s="23"/>
+      <c r="H435" s="23"/>
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A436" s="20"/>
-      <c r="G436" s="21"/>
-      <c r="H436" s="21"/>
+      <c r="A436" s="22"/>
+      <c r="G436" s="23"/>
+      <c r="H436" s="23"/>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="20"/>
-      <c r="G437" s="21"/>
-      <c r="H437" s="21"/>
+      <c r="A437" s="22"/>
+      <c r="G437" s="23"/>
+      <c r="H437" s="23"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="20"/>
-      <c r="G438" s="21"/>
-      <c r="H438" s="21"/>
+      <c r="A438" s="22"/>
+      <c r="G438" s="23"/>
+      <c r="H438" s="23"/>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A439" s="20"/>
-      <c r="G439" s="21"/>
-      <c r="H439" s="21"/>
+      <c r="A439" s="22"/>
+      <c r="G439" s="23"/>
+      <c r="H439" s="23"/>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A440" s="20"/>
-      <c r="G440" s="21"/>
-      <c r="H440" s="21"/>
+      <c r="A440" s="22"/>
+      <c r="G440" s="23"/>
+      <c r="H440" s="23"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A441" s="20"/>
-      <c r="G441" s="21"/>
-      <c r="H441" s="21"/>
+      <c r="A441" s="22"/>
+      <c r="G441" s="23"/>
+      <c r="H441" s="23"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="20"/>
-      <c r="G442" s="21"/>
-      <c r="H442" s="21"/>
+      <c r="A442" s="22"/>
+      <c r="G442" s="23"/>
+      <c r="H442" s="23"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="20"/>
-      <c r="G443" s="21"/>
-      <c r="H443" s="21"/>
+      <c r="A443" s="22"/>
+      <c r="G443" s="23"/>
+      <c r="H443" s="23"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="20"/>
-      <c r="G444" s="21"/>
-      <c r="H444" s="21"/>
+      <c r="A444" s="22"/>
+      <c r="G444" s="23"/>
+      <c r="H444" s="23"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="20"/>
-      <c r="G445" s="21"/>
-      <c r="H445" s="21"/>
+      <c r="A445" s="22"/>
+      <c r="G445" s="23"/>
+      <c r="H445" s="23"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="20"/>
-      <c r="G446" s="21"/>
-      <c r="H446" s="21"/>
+      <c r="A446" s="22"/>
+      <c r="G446" s="23"/>
+      <c r="H446" s="23"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="20"/>
-      <c r="G447" s="21"/>
-      <c r="H447" s="21"/>
+      <c r="A447" s="22"/>
+      <c r="G447" s="23"/>
+      <c r="H447" s="23"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="20"/>
-      <c r="G448" s="21"/>
-      <c r="H448" s="21"/>
+      <c r="A448" s="22"/>
+      <c r="G448" s="23"/>
+      <c r="H448" s="23"/>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A449" s="20"/>
-      <c r="G449" s="21"/>
-      <c r="H449" s="21"/>
+      <c r="A449" s="22"/>
+      <c r="G449" s="23"/>
+      <c r="H449" s="23"/>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A450" s="20"/>
-      <c r="G450" s="21"/>
-      <c r="H450" s="21"/>
+      <c r="A450" s="22"/>
+      <c r="G450" s="23"/>
+      <c r="H450" s="23"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A451" s="20"/>
-      <c r="G451" s="21"/>
-      <c r="H451" s="21"/>
+      <c r="A451" s="22"/>
+      <c r="G451" s="23"/>
+      <c r="H451" s="23"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="20"/>
-      <c r="G452" s="21"/>
-      <c r="H452" s="21"/>
+      <c r="A452" s="22"/>
+      <c r="G452" s="23"/>
+      <c r="H452" s="23"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="20"/>
-      <c r="G453" s="21"/>
-      <c r="H453" s="21"/>
+      <c r="A453" s="22"/>
+      <c r="G453" s="23"/>
+      <c r="H453" s="23"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="20"/>
-      <c r="G454" s="21"/>
-      <c r="H454" s="21"/>
+      <c r="A454" s="22"/>
+      <c r="G454" s="23"/>
+      <c r="H454" s="23"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A455" s="20"/>
-      <c r="G455" s="21"/>
-      <c r="H455" s="21"/>
+      <c r="A455" s="22"/>
+      <c r="G455" s="23"/>
+      <c r="H455" s="23"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A456" s="20"/>
-      <c r="G456" s="21"/>
-      <c r="H456" s="21"/>
+      <c r="A456" s="22"/>
+      <c r="G456" s="23"/>
+      <c r="H456" s="23"/>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A457" s="20"/>
-      <c r="G457" s="21"/>
-      <c r="H457" s="21"/>
+      <c r="A457" s="22"/>
+      <c r="G457" s="23"/>
+      <c r="H457" s="23"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="20"/>
-      <c r="G458" s="21"/>
-      <c r="H458" s="21"/>
+      <c r="A458" s="22"/>
+      <c r="G458" s="23"/>
+      <c r="H458" s="23"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="20"/>
-      <c r="G459" s="21"/>
-      <c r="H459" s="21"/>
+      <c r="A459" s="22"/>
+      <c r="G459" s="23"/>
+      <c r="H459" s="23"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="20"/>
-      <c r="G460" s="21"/>
-      <c r="H460" s="21"/>
+      <c r="A460" s="22"/>
+      <c r="G460" s="23"/>
+      <c r="H460" s="23"/>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="20"/>
-      <c r="G461" s="21"/>
-      <c r="H461" s="21"/>
+      <c r="A461" s="22"/>
+      <c r="G461" s="23"/>
+      <c r="H461" s="23"/>
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="20"/>
-      <c r="G462" s="21"/>
-      <c r="H462" s="21"/>
+      <c r="A462" s="22"/>
+      <c r="G462" s="23"/>
+      <c r="H462" s="23"/>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="20"/>
-      <c r="G463" s="21"/>
-      <c r="H463" s="21"/>
+      <c r="A463" s="22"/>
+      <c r="G463" s="23"/>
+      <c r="H463" s="23"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="20"/>
-      <c r="G464" s="21"/>
-      <c r="H464" s="21"/>
+      <c r="A464" s="22"/>
+      <c r="G464" s="23"/>
+      <c r="H464" s="23"/>
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="20"/>
-      <c r="G465" s="21"/>
-      <c r="H465" s="21"/>
+      <c r="A465" s="22"/>
+      <c r="G465" s="23"/>
+      <c r="H465" s="23"/>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="20"/>
-      <c r="G466" s="21"/>
-      <c r="H466" s="21"/>
+      <c r="A466" s="22"/>
+      <c r="G466" s="23"/>
+      <c r="H466" s="23"/>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="20"/>
-      <c r="G467" s="21"/>
-      <c r="H467" s="21"/>
+      <c r="A467" s="22"/>
+      <c r="G467" s="23"/>
+      <c r="H467" s="23"/>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="20"/>
-      <c r="G468" s="21"/>
-      <c r="H468" s="21"/>
+      <c r="A468" s="22"/>
+      <c r="G468" s="23"/>
+      <c r="H468" s="23"/>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="20"/>
-      <c r="G469" s="21"/>
-      <c r="H469" s="21"/>
+      <c r="A469" s="22"/>
+      <c r="G469" s="23"/>
+      <c r="H469" s="23"/>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="20"/>
-      <c r="G470" s="21"/>
-      <c r="H470" s="21"/>
+      <c r="A470" s="22"/>
+      <c r="G470" s="23"/>
+      <c r="H470" s="23"/>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="20"/>
-      <c r="G471" s="21"/>
-      <c r="H471" s="21"/>
+      <c r="A471" s="22"/>
+      <c r="G471" s="23"/>
+      <c r="H471" s="23"/>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="20"/>
-      <c r="G472" s="21"/>
-      <c r="H472" s="21"/>
+      <c r="A472" s="22"/>
+      <c r="G472" s="23"/>
+      <c r="H472" s="23"/>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="20"/>
-      <c r="G473" s="21"/>
-      <c r="H473" s="21"/>
+      <c r="A473" s="22"/>
+      <c r="G473" s="23"/>
+      <c r="H473" s="23"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="20"/>
-      <c r="G474" s="21"/>
-      <c r="H474" s="21"/>
+      <c r="A474" s="22"/>
+      <c r="G474" s="23"/>
+      <c r="H474" s="23"/>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="20"/>
-      <c r="G475" s="21"/>
-      <c r="H475" s="21"/>
+      <c r="A475" s="22"/>
+      <c r="G475" s="23"/>
+      <c r="H475" s="23"/>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="20"/>
-      <c r="G476" s="21"/>
-      <c r="H476" s="21"/>
+      <c r="A476" s="22"/>
+      <c r="G476" s="23"/>
+      <c r="H476" s="23"/>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="20"/>
-      <c r="G477" s="21"/>
-      <c r="H477" s="21"/>
+      <c r="A477" s="22"/>
+      <c r="G477" s="23"/>
+      <c r="H477" s="23"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A478" s="20"/>
-      <c r="G478" s="21"/>
-      <c r="H478" s="21"/>
+      <c r="A478" s="22"/>
+      <c r="G478" s="23"/>
+      <c r="H478" s="23"/>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="20"/>
-      <c r="G479" s="21"/>
-      <c r="H479" s="21"/>
+      <c r="A479" s="22"/>
+      <c r="G479" s="23"/>
+      <c r="H479" s="23"/>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="20"/>
-      <c r="G480" s="21"/>
-      <c r="H480" s="21"/>
+      <c r="A480" s="22"/>
+      <c r="G480" s="23"/>
+      <c r="H480" s="23"/>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="20"/>
-      <c r="G481" s="21"/>
-      <c r="H481" s="21"/>
+      <c r="A481" s="22"/>
+      <c r="G481" s="23"/>
+      <c r="H481" s="23"/>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="20"/>
-      <c r="G482" s="21"/>
-      <c r="H482" s="21"/>
+      <c r="A482" s="22"/>
+      <c r="G482" s="23"/>
+      <c r="H482" s="23"/>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A483" s="20"/>
-      <c r="G483" s="21"/>
-      <c r="H483" s="21"/>
+      <c r="A483" s="22"/>
+      <c r="G483" s="23"/>
+      <c r="H483" s="23"/>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A484" s="20"/>
-      <c r="G484" s="21"/>
-      <c r="H484" s="21"/>
+      <c r="A484" s="22"/>
+      <c r="G484" s="23"/>
+      <c r="H484" s="23"/>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A485" s="20"/>
-      <c r="G485" s="21"/>
-      <c r="H485" s="21"/>
+      <c r="A485" s="22"/>
+      <c r="G485" s="23"/>
+      <c r="H485" s="23"/>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A486" s="20"/>
-      <c r="G486" s="21"/>
-      <c r="H486" s="21"/>
+      <c r="A486" s="22"/>
+      <c r="G486" s="23"/>
+      <c r="H486" s="23"/>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="20"/>
-      <c r="G487" s="21"/>
-      <c r="H487" s="21"/>
+      <c r="A487" s="22"/>
+      <c r="G487" s="23"/>
+      <c r="H487" s="23"/>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="20"/>
-      <c r="G488" s="21"/>
-      <c r="H488" s="21"/>
+      <c r="A488" s="22"/>
+      <c r="G488" s="23"/>
+      <c r="H488" s="23"/>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="20"/>
-      <c r="G489" s="21"/>
-      <c r="H489" s="21"/>
+      <c r="A489" s="22"/>
+      <c r="G489" s="23"/>
+      <c r="H489" s="23"/>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="20"/>
-      <c r="G490" s="21"/>
-      <c r="H490" s="21"/>
+      <c r="A490" s="22"/>
+      <c r="G490" s="23"/>
+      <c r="H490" s="23"/>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A491" s="20"/>
-      <c r="G491" s="21"/>
-      <c r="H491" s="21"/>
+      <c r="A491" s="22"/>
+      <c r="G491" s="23"/>
+      <c r="H491" s="23"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A492" s="20"/>
-      <c r="G492" s="21"/>
-      <c r="H492" s="21"/>
+      <c r="A492" s="22"/>
+      <c r="G492" s="23"/>
+      <c r="H492" s="23"/>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A493" s="20"/>
-      <c r="G493" s="21"/>
-      <c r="H493" s="21"/>
+      <c r="A493" s="22"/>
+      <c r="G493" s="23"/>
+      <c r="H493" s="23"/>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A494" s="20"/>
-      <c r="G494" s="21"/>
-      <c r="H494" s="21"/>
+      <c r="A494" s="22"/>
+      <c r="G494" s="23"/>
+      <c r="H494" s="23"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A495" s="20"/>
-      <c r="G495" s="21"/>
-      <c r="H495" s="21"/>
+      <c r="A495" s="22"/>
+      <c r="G495" s="23"/>
+      <c r="H495" s="23"/>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A496" s="20"/>
-      <c r="G496" s="21"/>
-      <c r="H496" s="21"/>
+      <c r="A496" s="22"/>
+      <c r="G496" s="23"/>
+      <c r="H496" s="23"/>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A497" s="20"/>
-      <c r="G497" s="21"/>
-      <c r="H497" s="21"/>
+      <c r="A497" s="22"/>
+      <c r="G497" s="23"/>
+      <c r="H497" s="23"/>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A498" s="20"/>
-      <c r="G498" s="21"/>
-      <c r="H498" s="21"/>
+      <c r="A498" s="22"/>
+      <c r="G498" s="23"/>
+      <c r="H498" s="23"/>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="20"/>
-      <c r="G499" s="21"/>
-      <c r="H499" s="21"/>
+      <c r="A499" s="22"/>
+      <c r="G499" s="23"/>
+      <c r="H499" s="23"/>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="20"/>
-      <c r="G500" s="21"/>
-      <c r="H500" s="21"/>
+      <c r="A500" s="22"/>
+      <c r="G500" s="23"/>
+      <c r="H500" s="23"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -6737,433 +8080,433 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>96</v>
+        <v>312</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>97</v>
+        <v>313</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>98</v>
+        <v>314</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>99</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>100</v>
+        <v>316</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>102</v>
+        <v>317</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>103</v>
+        <v>318</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>104</v>
+        <v>319</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>105</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>106</v>
+        <v>321</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>108</v>
+        <v>323</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>109</v>
+        <v>324</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>110</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>111</v>
+        <v>326</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>112</v>
+        <v>327</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>108</v>
+        <v>323</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>113</v>
+        <v>328</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>114</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>330</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>116</v>
+        <v>331</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>117</v>
+        <v>332</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>118</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>119</v>
+        <v>334</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>120</v>
+        <v>335</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>122</v>
+        <v>337</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>123</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>124</v>
+        <v>339</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>125</v>
+        <v>340</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>126</v>
+        <v>341</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>127</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>128</v>
+        <v>343</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>130</v>
+        <v>344</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>103</v>
+        <v>318</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>131</v>
+        <v>345</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>132</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>134</v>
+        <v>348</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>135</v>
+        <v>349</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>136</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>137</v>
+        <v>351</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>138</v>
+        <v>352</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>139</v>
+        <v>353</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>140</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>141</v>
+        <v>355</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>142</v>
+        <v>239</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>143</v>
+        <v>356</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>144</v>
+        <v>357</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>145</v>
+        <v>358</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>146</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>149</v>
+        <v>362</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>151</v>
+        <v>364</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>152</v>
+        <v>365</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>130</v>
+        <v>344</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>153</v>
+        <v>366</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>154</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>155</v>
+        <v>368</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>156</v>
+        <v>369</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>157</v>
+        <v>370</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>158</v>
+        <v>371</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>159</v>
+        <v>372</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>161</v>
+        <v>374</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>157</v>
+        <v>370</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>163</v>
+        <v>376</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>164</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>165</v>
+        <v>378</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>157</v>
+        <v>370</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>166</v>
+        <v>379</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>167</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>168</v>
+        <v>381</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>169</v>
+        <v>382</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>170</v>
+        <v>383</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>171</v>
+        <v>384</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>172</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>173</v>
+        <v>386</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>174</v>
+        <v>387</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>175</v>
+        <v>388</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>108</v>
+        <v>323</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>176</v>
+        <v>389</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>177</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>178</v>
+        <v>391</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>179</v>
+        <v>392</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>180</v>
+        <v>393</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>181</v>
+        <v>394</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>182</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>183</v>
+        <v>396</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>184</v>
+        <v>397</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>185</v>
+        <v>398</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>186</v>
+        <v>399</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>187</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>188</v>
+        <v>401</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>189</v>
+        <v>402</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>190</v>
+        <v>403</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>191</v>
+        <v>404</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>192</v>
+        <v>405</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>193</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="A23" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7197,22 +8540,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>408</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>196</v>
+        <v>409</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>197</v>
+        <v>410</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>198</v>
+        <v>411</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>200</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7220,19 +8563,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>201</v>
+        <v>414</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>202</v>
+        <v>415</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>204</v>
+        <v>416</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>417</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>205</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7240,19 +8583,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>206</v>
+        <v>419</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>207</v>
+        <v>420</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>209</v>
+        <v>421</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>422</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>210</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7260,17 +8603,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>211</v>
+        <v>424</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>212</v>
+        <v>425</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9" t="s">
-        <v>214</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7278,19 +8621,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>215</v>
+        <v>428</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>216</v>
+        <v>429</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>217</v>
+        <v>426</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>430</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>218</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7298,19 +8641,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>219</v>
+        <v>432</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>220</v>
+        <v>433</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>221</v>
+        <v>426</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>434</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>222</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7318,19 +8661,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>223</v>
+        <v>436</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>224</v>
+        <v>437</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>226</v>
+        <v>438</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>439</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>227</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7338,19 +8681,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>228</v>
+        <v>441</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>229</v>
+        <v>442</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>230</v>
+        <v>426</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>443</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>231</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7358,19 +8701,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>232</v>
+        <v>445</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>233</v>
+        <v>446</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>234</v>
+        <v>426</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>447</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>235</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7378,19 +8721,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>236</v>
+        <v>449</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>237</v>
+        <v>450</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>238</v>
+        <v>426</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>239</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7398,19 +8741,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>240</v>
+        <v>453</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>241</v>
+        <v>454</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>243</v>
+        <v>455</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>456</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>244</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7418,19 +8761,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>245</v>
+        <v>458</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>246</v>
+        <v>459</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>248</v>
+        <v>460</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>461</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>249</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7438,19 +8781,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>250</v>
+        <v>463</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>251</v>
+        <v>464</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>253</v>
+        <v>465</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>466</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>254</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7458,19 +8801,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>255</v>
+        <v>468</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>256</v>
+        <v>469</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>257</v>
+        <v>426</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>470</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>258</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -7515,19 +8858,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>259</v>
+        <v>472</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>260</v>
+        <v>473</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>261</v>
+        <v>474</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>262</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7535,16 +8878,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>265</v>
+        <v>477</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>478</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>266</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7552,16 +8895,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>267</v>
+        <v>480</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>257</v>
+        <v>481</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>470</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>269</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7569,14 +8912,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>270</v>
+        <v>483</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>271</v>
+        <v>484</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
-        <v>272</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7584,16 +8927,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>275</v>
+        <v>487</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>488</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>276</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7601,16 +8944,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>277</v>
+        <v>490</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>279</v>
+        <v>491</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>492</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>280</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7618,16 +8961,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>281</v>
+        <v>494</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>283</v>
+        <v>495</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>496</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>284</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7635,14 +8978,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>285</v>
+        <v>498</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>286</v>
+        <v>499</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>287</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7650,65 +8993,65 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>288</v>
+        <v>501</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>289</v>
+        <v>502</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
-        <v>290</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>291</v>
+      <c r="A11" s="16" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>505</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="26" t="s">
+        <v>509</v>
+      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
